--- a/ORDER_MGMT/regular_order_mgmt/order_files/Mapped_Expired_OrderBook_Equity_10aug26_Mon.xlsx
+++ b/ORDER_MGMT/regular_order_mgmt/order_files/Mapped_Expired_OrderBook_Equity_10aug26_Mon.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\python\stocks\ORDER_MGMT\regular_order_mgmt\order_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33D8FAC2-F242-484C-9CC9-EE0224C7DFB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21DB09EB-0C7B-4AC8-BB55-01BF62A4A6AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$Z$222</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$Z$217</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$G$1:$G$218</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1578" uniqueCount="202">
   <si>
     <t>Date</t>
   </si>
@@ -1078,8 +1078,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:Z1000"/>
+  <dimension ref="A1:Z995"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.7265625" customWidth="1"/>
@@ -1132,30 +1131,30 @@
       <c r="Y1" s="13"/>
       <c r="Z1" s="13"/>
     </row>
-    <row r="2" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="15" t="s">
-        <v>189</v>
+    <row r="2" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="5">
+        <v>46244.645601851851</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D2" s="7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E2" s="7">
-        <v>3914</v>
+        <v>1162</v>
       </c>
       <c r="F2" s="7">
-        <v>-20.11918854</v>
+        <v>-1.1063829789999999</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="H2" s="14">
-        <v>4899.8</v>
+        <v>1175</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>8</v>
@@ -1178,30 +1177,30 @@
       <c r="Y2" s="13"/>
       <c r="Z2" s="13"/>
     </row>
-    <row r="3" spans="1:26" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="5">
-        <v>46244.767407407409</v>
+        <v>46244.645636574074</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="7">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E3" s="7">
-        <v>660</v>
+        <v>917</v>
       </c>
       <c r="F3" s="7">
-        <v>-19.805589309999998</v>
+        <v>-1.2385568119999999</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="H3" s="14">
-        <v>823</v>
+        <v>928.5</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>8</v>
@@ -1224,30 +1223,30 @@
       <c r="Y3" s="13"/>
       <c r="Z3" s="13"/>
     </row>
-    <row r="4" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="15" t="s">
-        <v>189</v>
+    <row r="4" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="5">
+        <v>46244.645636574074</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="7">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="E4" s="7">
-        <v>4014</v>
+        <v>227.5</v>
       </c>
       <c r="F4" s="7">
-        <v>-18.078288910000001</v>
+        <v>-1.301518438</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="H4" s="14">
-        <v>4899.8</v>
+        <v>230.5</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>8</v>
@@ -1270,30 +1269,30 @@
       <c r="Y4" s="13"/>
       <c r="Z4" s="13"/>
     </row>
-    <row r="5" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="15" t="s">
-        <v>189</v>
+    <row r="5" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="5">
+        <v>46244.645648148151</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="7">
-        <v>29</v>
+        <v>100</v>
       </c>
       <c r="E5" s="7">
-        <v>401</v>
+        <v>87.3</v>
       </c>
       <c r="F5" s="7">
-        <v>-17.148760330000002</v>
+        <v>-1.322482197</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
       <c r="H5" s="14">
-        <v>484</v>
+        <v>88.47</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>8</v>
@@ -1316,30 +1315,30 @@
       <c r="Y5" s="13"/>
       <c r="Z5" s="13"/>
     </row>
-    <row r="6" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="5">
-        <v>46239.789560185185</v>
+        <v>46244.76730324074</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D6" s="7">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E6" s="7">
-        <v>336</v>
+        <v>2552</v>
       </c>
       <c r="F6" s="7">
-        <v>-15.89486859</v>
+        <v>-1.5811801000000001</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="H6" s="14">
-        <v>399.5</v>
+        <v>2593</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>8</v>
@@ -1362,30 +1361,30 @@
       <c r="Y6" s="13"/>
       <c r="Z6" s="13"/>
     </row>
-    <row r="7" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="15" t="s">
-        <v>189</v>
+    <row r="7" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="5">
+        <v>46244.767592592594</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="7">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E7" s="7">
-        <v>4164</v>
+        <v>882</v>
       </c>
       <c r="F7" s="7">
-        <v>-15.016939470000001</v>
+        <v>-1.661277734</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="H7" s="14">
-        <v>4899.8</v>
+        <v>896.9</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>8</v>
@@ -1408,30 +1407,30 @@
       <c r="Y7" s="13"/>
       <c r="Z7" s="13"/>
     </row>
-    <row r="8" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="15" t="s">
-        <v>189</v>
+    <row r="8" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="5">
+        <v>46244.767326388886</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="7">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="E8" s="7">
-        <v>701</v>
+        <v>348</v>
       </c>
       <c r="F8" s="7">
-        <v>-13.72307692</v>
+        <v>-1.8058690740000001</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>192</v>
+        <v>150</v>
       </c>
       <c r="H8" s="14">
-        <v>812.5</v>
+        <v>354.4</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>8</v>
@@ -1454,30 +1453,30 @@
       <c r="Y8" s="13"/>
       <c r="Z8" s="13"/>
     </row>
-    <row r="9" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="5">
-        <v>46239.789560185185</v>
+        <v>46244.767418981479</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D9" s="7">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="E9" s="7">
-        <v>419</v>
+        <v>201</v>
       </c>
       <c r="F9" s="7">
-        <v>-13.429752069999999</v>
+        <v>-1.8794239690000001</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>190</v>
+        <v>145</v>
       </c>
       <c r="H9" s="14">
-        <v>484</v>
+        <v>204.85</v>
       </c>
       <c r="I9" s="6" t="s">
         <v>8</v>
@@ -1500,30 +1499,30 @@
       <c r="Y9" s="13"/>
       <c r="Z9" s="13"/>
     </row>
-    <row r="10" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="5">
-        <v>46241.765439814815</v>
+        <v>46244.76730324074</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="7">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="E10" s="7">
-        <v>352</v>
+        <v>128</v>
       </c>
       <c r="F10" s="7">
-        <v>-11.88986233</v>
+        <v>-1.8931555149999999</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H10" s="14">
-        <v>399.5</v>
+        <v>130.47</v>
       </c>
       <c r="I10" s="6" t="s">
         <v>8</v>
@@ -1546,30 +1545,30 @@
       <c r="Y10" s="13"/>
       <c r="Z10" s="13"/>
     </row>
-    <row r="11" spans="1:26" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="15" t="s">
-        <v>189</v>
+    <row r="11" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="5">
+        <v>46244.645590277774</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D11" s="7">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="E11" s="7">
-        <v>31.01</v>
+        <v>1152</v>
       </c>
       <c r="F11" s="7">
-        <v>-11.70273349</v>
+        <v>-1.9574468089999999</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="H11" s="14">
-        <v>35.119999999999997</v>
+        <v>1175</v>
       </c>
       <c r="I11" s="6" t="s">
         <v>8</v>
@@ -1592,30 +1591,30 @@
       <c r="Y11" s="13"/>
       <c r="Z11" s="13"/>
     </row>
-    <row r="12" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="5">
-        <v>46240.688009259262</v>
+        <v>46241.765462962961</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D12" s="7">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="E12" s="7">
-        <v>111</v>
+        <v>2264</v>
       </c>
       <c r="F12" s="7">
-        <v>-10.936371660000001</v>
+        <v>-1.9913419910000001</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>148</v>
+        <v>191</v>
       </c>
       <c r="H12" s="14">
-        <v>124.63</v>
+        <v>2310</v>
       </c>
       <c r="I12" s="6" t="s">
         <v>8</v>
@@ -1638,30 +1637,30 @@
       <c r="Y12" s="13"/>
       <c r="Z12" s="13"/>
     </row>
-    <row r="13" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="15" t="s">
-        <v>189</v>
+    <row r="13" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="5">
+        <v>46244.645613425928</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D13" s="7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E13" s="7">
-        <v>4364</v>
+        <v>712</v>
       </c>
       <c r="F13" s="7">
-        <v>-10.93514021</v>
+        <v>-1.9958706129999999</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="H13" s="14">
-        <v>4899.8</v>
+        <v>726.5</v>
       </c>
       <c r="I13" s="6" t="s">
         <v>8</v>
@@ -1684,30 +1683,30 @@
       <c r="Y13" s="13"/>
       <c r="Z13" s="13"/>
     </row>
-    <row r="14" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="15" t="s">
-        <v>189</v>
+    <row r="14" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="5">
+        <v>46244.76730324074</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E14" s="7">
-        <v>2064</v>
+        <v>2540</v>
       </c>
       <c r="F14" s="7">
-        <v>-10.649350650000001</v>
+        <v>-2.0439645199999998</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>191</v>
+        <v>144</v>
       </c>
       <c r="H14" s="14">
-        <v>2310</v>
+        <v>2593</v>
       </c>
       <c r="I14" s="6" t="s">
         <v>8</v>
@@ -1730,30 +1729,30 @@
       <c r="Y14" s="13"/>
       <c r="Z14" s="13"/>
     </row>
-    <row r="15" spans="1:26" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:26" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="5">
-        <v>46239.63553240741</v>
+        <v>46244.76730324074</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="7">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="E15" s="7">
-        <v>4415</v>
+        <v>436</v>
       </c>
       <c r="F15" s="7">
-        <v>-10.426261439999999</v>
+        <v>-2.1873247340000002</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>184</v>
+        <v>149</v>
       </c>
       <c r="H15" s="14">
-        <v>4928.8999999999996</v>
+        <v>445.75</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>8</v>
@@ -1776,30 +1775,30 @@
       <c r="Y15" s="13"/>
       <c r="Z15" s="13"/>
     </row>
-    <row r="16" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="5">
-        <v>46241.688090277778</v>
+        <v>46244.645613425928</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D16" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="7">
-        <v>4410</v>
+        <v>1302</v>
       </c>
       <c r="F16" s="7">
-        <v>-9.9963263809999994</v>
+        <v>-2.2889305819999999</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="H16" s="14">
-        <v>4899.8</v>
+        <v>1332.5</v>
       </c>
       <c r="I16" s="6" t="s">
         <v>8</v>
@@ -1822,30 +1821,30 @@
       <c r="Y16" s="13"/>
       <c r="Z16" s="13"/>
     </row>
-    <row r="17" spans="1:26" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="5">
-        <v>46241.765462962961</v>
+        <v>46244.645601851851</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D17" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E17" s="7">
-        <v>1751</v>
+        <v>1188</v>
       </c>
       <c r="F17" s="7">
-        <v>-9.9789213920000002</v>
+        <v>-2.7027027029999999</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="H17" s="14">
-        <v>1945.1</v>
+        <v>1221</v>
       </c>
       <c r="I17" s="6" t="s">
         <v>8</v>
@@ -1868,30 +1867,30 @@
       <c r="Y17" s="13"/>
       <c r="Z17" s="13"/>
     </row>
-    <row r="18" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="15" t="s">
-        <v>189</v>
+    <row r="18" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="5">
+        <v>46244.645601851851</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D18" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E18" s="7">
-        <v>4010</v>
+        <v>2938</v>
       </c>
       <c r="F18" s="7">
-        <v>-9.9685675800000002</v>
+        <v>-2.7152317880000001</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H18" s="14">
-        <v>4454</v>
+        <v>3020</v>
       </c>
       <c r="I18" s="6" t="s">
         <v>8</v>
@@ -1914,30 +1913,30 @@
       <c r="Y18" s="13"/>
       <c r="Z18" s="13"/>
     </row>
-    <row r="19" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="5">
-        <v>46241.688136574077</v>
+        <v>46181.6875</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D19" s="7">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="E19" s="7">
-        <v>620</v>
+        <v>136.15</v>
       </c>
       <c r="F19" s="7">
-        <v>-9.8444088989999994</v>
+        <v>-2.75</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>151</v>
+        <v>198</v>
       </c>
       <c r="H19" s="14">
-        <v>687.7</v>
+        <v>140</v>
       </c>
       <c r="I19" s="6" t="s">
         <v>8</v>
@@ -1960,30 +1959,30 @@
       <c r="Y19" s="13"/>
       <c r="Z19" s="13"/>
     </row>
-    <row r="20" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="5">
-        <v>46240.688055555554</v>
+        <v>46244.645590277774</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D20" s="7">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E20" s="7">
-        <v>620</v>
+        <v>1142</v>
       </c>
       <c r="F20" s="7">
-        <v>-9.8444088989999994</v>
+        <v>-2.808510638</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="H20" s="14">
-        <v>687.7</v>
+        <v>1175</v>
       </c>
       <c r="I20" s="6" t="s">
         <v>8</v>
@@ -2006,30 +2005,30 @@
       <c r="Y20" s="13"/>
       <c r="Z20" s="13"/>
     </row>
-    <row r="21" spans="1:26" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="15" t="s">
-        <v>189</v>
+    <row r="21" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="5">
+        <v>46181.6875</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D21" s="7">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E21" s="7">
-        <v>6920</v>
+        <v>344</v>
       </c>
       <c r="F21" s="7">
-        <v>-9.8018769549999991</v>
+        <v>-2.9345372460000001</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H21" s="14">
-        <v>7672</v>
+        <v>354.4</v>
       </c>
       <c r="I21" s="6" t="s">
         <v>8</v>
@@ -2052,30 +2051,30 @@
       <c r="Y21" s="13"/>
       <c r="Z21" s="13"/>
     </row>
-    <row r="22" spans="1:26" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:26" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="5">
-        <v>46240.635555555556</v>
+        <v>46244.767326388886</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D22" s="7">
-        <v>2</v>
+        <v>150</v>
       </c>
       <c r="E22" s="7">
-        <v>4456</v>
+        <v>214</v>
       </c>
       <c r="F22" s="7">
-        <v>-9.5944328349999992</v>
+        <v>-2.9654484449999998</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="H22" s="14">
-        <v>4928.8999999999996</v>
+        <v>220.54</v>
       </c>
       <c r="I22" s="6" t="s">
         <v>8</v>
@@ -2098,30 +2097,30 @@
       <c r="Y22" s="13"/>
       <c r="Z22" s="13"/>
     </row>
-    <row r="23" spans="1:26" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="5">
-        <v>46244.76730324074</v>
+        <v>46241.645509259259</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D23" s="7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E23" s="7">
-        <v>547</v>
+        <v>3950</v>
       </c>
       <c r="F23" s="7">
-        <v>-9.467063886</v>
+        <v>-3.0198870609999999</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="H23" s="14">
-        <v>604.20000000000005</v>
+        <v>4073</v>
       </c>
       <c r="I23" s="6" t="s">
         <v>8</v>
@@ -2144,30 +2143,30 @@
       <c r="Y23" s="13"/>
       <c r="Z23" s="13"/>
     </row>
-    <row r="24" spans="1:26" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="15" t="s">
-        <v>189</v>
+    <row r="24" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="5">
+        <v>46244.767384259256</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D24" s="7">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="E24" s="7">
-        <v>322</v>
+        <v>286</v>
       </c>
       <c r="F24" s="7">
-        <v>-9.1422121900000004</v>
+        <v>-3.0672767329999999</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="H24" s="14">
-        <v>354.4</v>
+        <v>295.05</v>
       </c>
       <c r="I24" s="6" t="s">
         <v>8</v>
@@ -2190,30 +2189,30 @@
       <c r="Y24" s="13"/>
       <c r="Z24" s="13"/>
     </row>
-    <row r="25" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="15" t="s">
-        <v>189</v>
+    <row r="25" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="5">
+        <v>46244.767326388886</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D25" s="7">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E25" s="7">
-        <v>4060</v>
+        <v>1666</v>
       </c>
       <c r="F25" s="7">
-        <v>-8.8459811409999993</v>
+        <v>-3.1395348840000001</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="H25" s="14">
-        <v>4454</v>
+        <v>1720</v>
       </c>
       <c r="I25" s="6" t="s">
         <v>8</v>
@@ -2236,30 +2235,30 @@
       <c r="Y25" s="13"/>
       <c r="Z25" s="13"/>
     </row>
-    <row r="26" spans="1:26" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="5">
-        <v>46239.789583333331</v>
+        <v>46241.765092592592</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D26" s="7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E26" s="7">
-        <v>411</v>
+        <v>2510</v>
       </c>
       <c r="F26" s="7">
-        <v>-8.46325167</v>
+        <v>-3.2009255689999998</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>194</v>
+        <v>144</v>
       </c>
       <c r="H26" s="14">
-        <v>449</v>
+        <v>2593</v>
       </c>
       <c r="I26" s="6" t="s">
         <v>8</v>
@@ -2282,30 +2281,30 @@
       <c r="Y26" s="13"/>
       <c r="Z26" s="13"/>
     </row>
-    <row r="27" spans="1:26" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="5">
-        <v>46240.687974537039</v>
+        <v>46244.63559027778</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D27" s="7">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E27" s="7">
-        <v>202</v>
+        <v>764</v>
       </c>
       <c r="F27" s="7">
-        <v>-8.4066382520000005</v>
+        <v>-3.2360205180000001</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="H27" s="14">
-        <v>220.54</v>
+        <v>789.55</v>
       </c>
       <c r="I27" s="6" t="s">
         <v>8</v>
@@ -2328,30 +2327,30 @@
       <c r="Y27" s="13"/>
       <c r="Z27" s="13"/>
     </row>
-    <row r="28" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="5">
-        <v>46211.765277777777</v>
+        <v>46244.635555555556</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D28" s="7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E28" s="7">
-        <v>366</v>
+        <v>2352</v>
       </c>
       <c r="F28" s="7">
-        <v>-8.3854818519999998</v>
+        <v>-3.265608292</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="H28" s="14">
-        <v>399.5</v>
+        <v>2431.4</v>
       </c>
       <c r="I28" s="6" t="s">
         <v>8</v>
@@ -2374,30 +2373,30 @@
       <c r="Y28" s="13"/>
       <c r="Z28" s="13"/>
     </row>
-    <row r="29" spans="1:26" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="15" t="s">
-        <v>189</v>
+    <row r="29" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="5">
+        <v>46244.63559027778</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D29" s="7">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E29" s="7">
-        <v>2552</v>
+        <v>850</v>
       </c>
       <c r="F29" s="7">
-        <v>-8.1022686349999997</v>
+        <v>-3.2882011609999999</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="H29" s="14">
-        <v>2777</v>
+        <v>878.9</v>
       </c>
       <c r="I29" s="6" t="s">
         <v>8</v>
@@ -2420,30 +2419,30 @@
       <c r="Y29" s="13"/>
       <c r="Z29" s="13"/>
     </row>
-    <row r="30" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="5">
-        <v>46244.63553240741</v>
+        <v>46244.63554398148</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D30" s="7">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="E30" s="7">
-        <v>2370</v>
+        <v>390</v>
       </c>
       <c r="F30" s="7">
-        <v>-8.0325960419999998</v>
+        <v>-3.3097805880000002</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H30" s="14">
-        <v>2577</v>
+        <v>403.35</v>
       </c>
       <c r="I30" s="6" t="s">
         <v>8</v>
@@ -2466,30 +2465,30 @@
       <c r="Y30" s="13"/>
       <c r="Z30" s="13"/>
     </row>
-    <row r="31" spans="1:26" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="5">
-        <v>46211.635416666664</v>
+        <v>46211.645138888889</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D31" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E31" s="7">
-        <v>3310</v>
+        <v>3938</v>
       </c>
       <c r="F31" s="7">
-        <v>-7.9737544480000002</v>
+        <v>-3.3145101889999999</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="H31" s="14">
-        <v>3596.8</v>
+        <v>4073</v>
       </c>
       <c r="I31" s="6" t="s">
         <v>8</v>
@@ -2512,30 +2511,30 @@
       <c r="Y31" s="13"/>
       <c r="Z31" s="13"/>
     </row>
-    <row r="32" spans="1:26" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="5">
-        <v>46244.63554398148</v>
+        <v>46244.63559027778</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D32" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32" s="7">
-        <v>2560</v>
+        <v>4306</v>
       </c>
       <c r="F32" s="7">
-        <v>-7.8141879730000001</v>
+        <v>-3.3228558600000002</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="H32" s="14">
-        <v>2777</v>
+        <v>4454</v>
       </c>
       <c r="I32" s="6" t="s">
         <v>8</v>
@@ -2558,30 +2557,30 @@
       <c r="Y32" s="13"/>
       <c r="Z32" s="13"/>
     </row>
-    <row r="33" spans="1:26" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="15" t="s">
         <v>189</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D33" s="7">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="E33" s="7">
-        <v>327</v>
+        <v>702</v>
       </c>
       <c r="F33" s="7">
-        <v>-7.7313769749999999</v>
+        <v>-3.372333104</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="H33" s="14">
-        <v>354.4</v>
+        <v>726.5</v>
       </c>
       <c r="I33" s="6" t="s">
         <v>8</v>
@@ -2604,30 +2603,30 @@
       <c r="Y33" s="13"/>
       <c r="Z33" s="13"/>
     </row>
-    <row r="34" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="15" t="s">
-        <v>189</v>
+    <row r="34" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="5">
+        <v>46244.635520833333</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D34" s="7">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="E34" s="7">
-        <v>4110</v>
+        <v>897</v>
       </c>
       <c r="F34" s="7">
-        <v>-7.7233947010000001</v>
+        <v>-3.3925686590000002</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="H34" s="14">
-        <v>4454</v>
+        <v>928.5</v>
       </c>
       <c r="I34" s="6" t="s">
         <v>8</v>
@@ -2650,30 +2649,30 @@
       <c r="Y34" s="13"/>
       <c r="Z34" s="13"/>
     </row>
-    <row r="35" spans="1:26" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="15" t="s">
-        <v>189</v>
+    <row r="35" spans="1:26" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="5">
+        <v>46244.63559027778</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D35" s="7">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E35" s="7">
-        <v>3760</v>
+        <v>1452</v>
       </c>
       <c r="F35" s="7">
-        <v>-7.6847532530000002</v>
+        <v>-3.406067057</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H35" s="14">
-        <v>4073</v>
+        <v>1503.2</v>
       </c>
       <c r="I35" s="6" t="s">
         <v>8</v>
@@ -2696,30 +2695,30 @@
       <c r="Y35" s="13"/>
       <c r="Z35" s="13"/>
     </row>
-    <row r="36" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="15" t="s">
-        <v>189</v>
+    <row r="36" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="5">
+        <v>46244.635520833333</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D36" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E36" s="7">
-        <v>812</v>
+        <v>1066</v>
       </c>
       <c r="F36" s="7">
-        <v>-7.6117874619999997</v>
+        <v>-3.5294117649999999</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="H36" s="14">
-        <v>878.9</v>
+        <v>1105</v>
       </c>
       <c r="I36" s="6" t="s">
         <v>8</v>
@@ -2742,30 +2741,30 @@
       <c r="Y36" s="13"/>
       <c r="Z36" s="13"/>
     </row>
-    <row r="37" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="15" t="s">
-        <v>189</v>
+    <row r="37" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="5">
+        <v>46241.63553240741</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D37" s="7">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E37" s="7">
-        <v>251</v>
+        <v>2460</v>
       </c>
       <c r="F37" s="7">
-        <v>-7.550644567</v>
+        <v>-3.6427732079999999</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="H37" s="14">
-        <v>271.5</v>
+        <v>2553</v>
       </c>
       <c r="I37" s="6" t="s">
         <v>8</v>
@@ -2788,30 +2787,30 @@
       <c r="Y37" s="13"/>
       <c r="Z37" s="13"/>
     </row>
-    <row r="38" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="5">
-        <v>46244.767395833333</v>
+        <v>46240.635578703703</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D38" s="7">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="E38" s="7">
-        <v>115.25</v>
+        <v>1132</v>
       </c>
       <c r="F38" s="7">
-        <v>-7.5262777820000002</v>
+        <v>-3.6595744680000002</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="H38" s="14">
-        <v>124.63</v>
+        <v>1175</v>
       </c>
       <c r="I38" s="6" t="s">
         <v>8</v>
@@ -2834,30 +2833,30 @@
       <c r="Y38" s="13"/>
       <c r="Z38" s="13"/>
     </row>
-    <row r="39" spans="1:26" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="5">
-        <v>46241.63553240741</v>
+        <v>46244.63553240741</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D39" s="7">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E39" s="7">
-        <v>4560</v>
+        <v>1260</v>
       </c>
       <c r="F39" s="7">
-        <v>-7.4844285739999998</v>
+        <v>-3.8167938929999998</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="H39" s="14">
-        <v>4928.8999999999996</v>
+        <v>1310</v>
       </c>
       <c r="I39" s="6" t="s">
         <v>8</v>
@@ -2880,30 +2879,30 @@
       <c r="Y39" s="13"/>
       <c r="Z39" s="13"/>
     </row>
-    <row r="40" spans="1:26" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="5">
-        <v>46240.635567129626</v>
+        <v>46244.635520833333</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D40" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E40" s="7">
-        <v>2251</v>
+        <v>1030</v>
       </c>
       <c r="F40" s="7">
-        <v>-7.4195936500000004</v>
+        <v>-3.828197946</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H40" s="14">
-        <v>2431.4</v>
+        <v>1071</v>
       </c>
       <c r="I40" s="6" t="s">
         <v>8</v>
@@ -2926,30 +2925,30 @@
       <c r="Y40" s="13"/>
       <c r="Z40" s="13"/>
     </row>
-    <row r="41" spans="1:26" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="5">
-        <v>46150.793055555558</v>
+        <v>46244.63553240741</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D41" s="7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E41" s="7">
-        <v>560</v>
+        <v>18052</v>
       </c>
       <c r="F41" s="7">
-        <v>-7.3154584570000001</v>
+        <v>-3.8354996799999999</v>
       </c>
       <c r="G41" s="13" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="H41" s="14">
-        <v>604.20000000000005</v>
+        <v>18772</v>
       </c>
       <c r="I41" s="6" t="s">
         <v>8</v>
@@ -2972,30 +2971,30 @@
       <c r="Y41" s="13"/>
       <c r="Z41" s="13"/>
     </row>
-    <row r="42" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:26" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" s="5">
-        <v>46241.688136574077</v>
+        <v>46244.767326388886</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D42" s="7">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E42" s="7">
-        <v>640</v>
+        <v>212</v>
       </c>
       <c r="F42" s="7">
-        <v>-6.9361640250000001</v>
+        <v>-3.8723134130000001</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H42" s="14">
-        <v>687.7</v>
+        <v>220.54</v>
       </c>
       <c r="I42" s="6" t="s">
         <v>8</v>
@@ -3018,30 +3017,30 @@
       <c r="Y42" s="13"/>
       <c r="Z42" s="13"/>
     </row>
-    <row r="43" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="5">
-        <v>46181.6875</v>
+        <v>46244.767326388886</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D43" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E43" s="7">
-        <v>640</v>
+        <v>4710</v>
       </c>
       <c r="F43" s="7">
-        <v>-6.9361640250000001</v>
+        <v>-3.873627495</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H43" s="14">
-        <v>687.7</v>
+        <v>4899.8</v>
       </c>
       <c r="I43" s="6" t="s">
         <v>8</v>
@@ -3064,30 +3063,30 @@
       <c r="Y43" s="13"/>
       <c r="Z43" s="13"/>
     </row>
-    <row r="44" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="5">
-        <v>46150.793055555558</v>
+        <v>46211.6875</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D44" s="7">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E44" s="7">
-        <v>640</v>
+        <v>2490</v>
       </c>
       <c r="F44" s="7">
-        <v>-6.9361640250000001</v>
+        <v>-3.9722329350000001</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="H44" s="14">
-        <v>687.7</v>
+        <v>2593</v>
       </c>
       <c r="I44" s="6" t="s">
         <v>8</v>
@@ -3110,30 +3109,30 @@
       <c r="Y44" s="13"/>
       <c r="Z44" s="13"/>
     </row>
-    <row r="45" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="5">
-        <v>46244.63554398148</v>
+        <v>46244.767326388886</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D45" s="7">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="E45" s="7">
-        <v>2401</v>
+        <v>340.2</v>
       </c>
       <c r="F45" s="7">
-        <v>-6.829646876</v>
+        <v>-4.0067720089999996</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>182</v>
+        <v>150</v>
       </c>
       <c r="H45" s="14">
-        <v>2577</v>
+        <v>354.4</v>
       </c>
       <c r="I45" s="6" t="s">
         <v>8</v>
@@ -3156,12 +3155,12 @@
       <c r="Y45" s="13"/>
       <c r="Z45" s="13"/>
     </row>
-    <row r="46" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="5">
-        <v>46211.765277777777</v>
+        <v>46244.767326388886</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>10</v>
@@ -3170,16 +3169,16 @@
         <v>5</v>
       </c>
       <c r="E46" s="7">
-        <v>452</v>
+        <v>660</v>
       </c>
       <c r="F46" s="7">
-        <v>-6.6115702479999996</v>
+        <v>-4.0279191509999999</v>
       </c>
       <c r="G46" s="13" t="s">
-        <v>190</v>
+        <v>151</v>
       </c>
       <c r="H46" s="14">
-        <v>484</v>
+        <v>687.7</v>
       </c>
       <c r="I46" s="6" t="s">
         <v>8</v>
@@ -3202,30 +3201,30 @@
       <c r="Y46" s="13"/>
       <c r="Z46" s="13"/>
     </row>
-    <row r="47" spans="1:26" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="15" t="s">
-        <v>189</v>
+    <row r="47" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="5">
+        <v>46244.767592592594</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D47" s="7">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="E47" s="7">
-        <v>331</v>
+        <v>860</v>
       </c>
       <c r="F47" s="7">
-        <v>-6.6027088039999997</v>
+        <v>-4.1141710339999999</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="H47" s="14">
-        <v>354.4</v>
+        <v>896.9</v>
       </c>
       <c r="I47" s="6" t="s">
         <v>8</v>
@@ -3248,30 +3247,30 @@
       <c r="Y47" s="13"/>
       <c r="Z47" s="13"/>
     </row>
-    <row r="48" spans="1:26" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A48" s="5">
-        <v>46211.6875</v>
+        <v>46211.635416666664</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D48" s="7">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="E48" s="7">
-        <v>206</v>
+        <v>1277</v>
       </c>
       <c r="F48" s="7">
-        <v>-6.5929083159999999</v>
+        <v>-4.1651031889999999</v>
       </c>
       <c r="G48" s="13" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H48" s="14">
-        <v>220.54</v>
+        <v>1332.5</v>
       </c>
       <c r="I48" s="6" t="s">
         <v>8</v>
@@ -3294,30 +3293,30 @@
       <c r="Y48" s="13"/>
       <c r="Z48" s="13"/>
     </row>
-    <row r="49" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:26" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="5">
-        <v>46211.635416666664</v>
+        <v>46244.63559027778</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D49" s="7">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E49" s="7">
-        <v>17552</v>
+        <v>1440</v>
       </c>
       <c r="F49" s="7">
-        <v>-6.4990411249999998</v>
+        <v>-4.2043640230000001</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="H49" s="14">
-        <v>18772</v>
+        <v>1503.2</v>
       </c>
       <c r="I49" s="6" t="s">
         <v>8</v>
@@ -3340,30 +3339,30 @@
       <c r="Y49" s="13"/>
       <c r="Z49" s="13"/>
     </row>
-    <row r="50" spans="1:26" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="15" t="s">
-        <v>189</v>
+    <row r="50" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="5">
+        <v>46244.767418981479</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D50" s="7">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="E50" s="7">
-        <v>3810</v>
+        <v>196</v>
       </c>
       <c r="F50" s="7">
-        <v>-6.457156887</v>
+        <v>-4.3202343179999998</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>172</v>
+        <v>145</v>
       </c>
       <c r="H50" s="14">
-        <v>4073</v>
+        <v>204.85</v>
       </c>
       <c r="I50" s="6" t="s">
         <v>8</v>
@@ -3386,12 +3385,12 @@
       <c r="Y50" s="13"/>
       <c r="Z50" s="13"/>
     </row>
-    <row r="51" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A51" s="5">
-        <v>46241.765462962961</v>
+        <v>46244.635509259257</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>10</v>
@@ -3400,16 +3399,16 @@
         <v>1</v>
       </c>
       <c r="E51" s="7">
-        <v>2164</v>
+        <v>13552</v>
       </c>
       <c r="F51" s="7">
-        <v>-6.3203463199999996</v>
+        <v>-4.3613267469999997</v>
       </c>
       <c r="G51" s="13" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="H51" s="14">
-        <v>2310</v>
+        <v>14170</v>
       </c>
       <c r="I51" s="6" t="s">
         <v>8</v>
@@ -3432,30 +3431,30 @@
       <c r="Y51" s="13"/>
       <c r="Z51" s="13"/>
     </row>
-    <row r="52" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A52" s="5">
-        <v>46240.687974537039</v>
+        <v>46211.635416666664</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D52" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E52" s="7">
-        <v>2164</v>
+        <v>2888</v>
       </c>
       <c r="F52" s="7">
-        <v>-6.3203463199999996</v>
+        <v>-4.3708609269999998</v>
       </c>
       <c r="G52" s="13" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="H52" s="14">
-        <v>2310</v>
+        <v>3020</v>
       </c>
       <c r="I52" s="6" t="s">
         <v>8</v>
@@ -3478,30 +3477,30 @@
       <c r="Y52" s="13"/>
       <c r="Z52" s="13"/>
     </row>
-    <row r="53" spans="1:26" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:26" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A53" s="5">
-        <v>46241.635567129626</v>
+        <v>46244.767326388886</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D53" s="7">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="E53" s="7">
-        <v>1410</v>
+        <v>426</v>
       </c>
       <c r="F53" s="7">
-        <v>-6.2001064399999999</v>
+        <v>-4.430734717</v>
       </c>
       <c r="G53" s="13" t="s">
-        <v>176</v>
+        <v>149</v>
       </c>
       <c r="H53" s="14">
-        <v>1503.2</v>
+        <v>445.75</v>
       </c>
       <c r="I53" s="6" t="s">
         <v>8</v>
@@ -3524,30 +3523,30 @@
       <c r="Y53" s="13"/>
       <c r="Z53" s="13"/>
     </row>
-    <row r="54" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A54" s="5">
-        <v>46181.6875</v>
+        <v>46211.765277777777</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D54" s="7">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E54" s="7">
-        <v>1614</v>
+        <v>190.1</v>
       </c>
       <c r="F54" s="7">
-        <v>-6.1627906980000002</v>
+        <v>-4.4819616120000001</v>
       </c>
       <c r="G54" s="13" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H54" s="14">
-        <v>1720</v>
+        <v>199.02</v>
       </c>
       <c r="I54" s="6" t="s">
         <v>8</v>
@@ -3570,30 +3569,30 @@
       <c r="Y54" s="13"/>
       <c r="Z54" s="13"/>
     </row>
-    <row r="55" spans="1:26" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A55" s="5">
-        <v>46239.635520833333</v>
+        <v>46244.63554398148</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D55" s="7">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E55" s="7">
-        <v>1005</v>
+        <v>1251</v>
       </c>
       <c r="F55" s="7">
-        <v>-6.1624649859999998</v>
+        <v>-4.5038167939999996</v>
       </c>
       <c r="G55" s="13" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="H55" s="14">
-        <v>1071</v>
+        <v>1310</v>
       </c>
       <c r="I55" s="6" t="s">
         <v>8</v>
@@ -3616,30 +3615,30 @@
       <c r="Y55" s="13"/>
       <c r="Z55" s="13"/>
     </row>
-    <row r="56" spans="1:26" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="15" t="s">
-        <v>189</v>
+    <row r="56" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A56" s="5">
+        <v>46211.635416666664</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D56" s="7">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="E56" s="7">
-        <v>277</v>
+        <v>1166</v>
       </c>
       <c r="F56" s="7">
-        <v>-6.1176071849999998</v>
+        <v>-4.5045045049999999</v>
       </c>
       <c r="G56" s="13" t="s">
-        <v>142</v>
+        <v>171</v>
       </c>
       <c r="H56" s="14">
-        <v>295.05</v>
+        <v>1221</v>
       </c>
       <c r="I56" s="6" t="s">
         <v>8</v>
@@ -3662,30 +3661,30 @@
       <c r="Y56" s="13"/>
       <c r="Z56" s="13"/>
     </row>
-    <row r="57" spans="1:26" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="5">
-        <v>46211.765277777777</v>
+    <row r="57" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A57" s="15" t="s">
+        <v>189</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D57" s="7">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E57" s="7">
-        <v>2435</v>
+        <v>220.1</v>
       </c>
       <c r="F57" s="7">
-        <v>-6.0933281910000003</v>
+        <v>-4.5119305860000001</v>
       </c>
       <c r="G57" s="13" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="H57" s="14">
-        <v>2593</v>
+        <v>230.5</v>
       </c>
       <c r="I57" s="6" t="s">
         <v>8</v>
@@ -3708,7 +3707,7 @@
       <c r="Y57" s="13"/>
       <c r="Z57" s="13"/>
     </row>
-    <row r="58" spans="1:26" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A58" s="15" t="s">
         <v>189</v>
       </c>
@@ -3719,13 +3718,13 @@
         <v>10</v>
       </c>
       <c r="D58" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E58" s="7">
-        <v>3830</v>
+        <v>3888</v>
       </c>
       <c r="F58" s="7">
-        <v>-5.9661183400000004</v>
+        <v>-4.5421065550000002</v>
       </c>
       <c r="G58" s="13" t="s">
         <v>172</v>
@@ -3754,30 +3753,30 @@
       <c r="Y58" s="13"/>
       <c r="Z58" s="13"/>
     </row>
-    <row r="59" spans="1:26" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:26" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A59" s="5">
-        <v>46244.63553240741</v>
+        <v>46244.63554398148</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D59" s="7">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E59" s="7">
-        <v>4640</v>
+        <v>1007</v>
       </c>
       <c r="F59" s="7">
-        <v>-5.8613483740000003</v>
+        <v>-4.5497630329999996</v>
       </c>
       <c r="G59" s="13" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H59" s="14">
-        <v>4928.8999999999996</v>
+        <v>1055</v>
       </c>
       <c r="I59" s="6" t="s">
         <v>8</v>
@@ -3800,12 +3799,12 @@
       <c r="Y59" s="13"/>
       <c r="Z59" s="13"/>
     </row>
-    <row r="60" spans="1:26" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A60" s="5">
-        <v>46240.687962962962</v>
+        <v>46241.635567129626</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>10</v>
@@ -3814,16 +3813,16 @@
         <v>5</v>
       </c>
       <c r="E60" s="7">
-        <v>569</v>
+        <v>838</v>
       </c>
       <c r="F60" s="7">
-        <v>-5.8258854680000001</v>
+        <v>-4.653544203</v>
       </c>
       <c r="G60" s="13" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="H60" s="14">
-        <v>604.20000000000005</v>
+        <v>878.9</v>
       </c>
       <c r="I60" s="6" t="s">
         <v>8</v>
@@ -3846,30 +3845,30 @@
       <c r="Y60" s="13"/>
       <c r="Z60" s="13"/>
     </row>
-    <row r="61" spans="1:26" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A61" s="5">
-        <v>46211.76458333333</v>
+        <v>46240.687962962962</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D61" s="7">
-        <v>500</v>
+        <v>5</v>
       </c>
       <c r="E61" s="7">
-        <v>33.159999999999997</v>
+        <v>2470</v>
       </c>
       <c r="F61" s="7">
-        <v>-5.5808656040000004</v>
+        <v>-4.7435403010000003</v>
       </c>
       <c r="G61" s="13" t="s">
-        <v>193</v>
+        <v>144</v>
       </c>
       <c r="H61" s="14">
-        <v>35.119999999999997</v>
+        <v>2593</v>
       </c>
       <c r="I61" s="6" t="s">
         <v>8</v>
@@ -3892,30 +3891,30 @@
       <c r="Y61" s="13"/>
       <c r="Z61" s="13"/>
     </row>
-    <row r="62" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="5">
-        <v>46211.635416666664</v>
+    <row r="62" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A62" s="15" t="s">
+        <v>189</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D62" s="7">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E62" s="7">
-        <v>4206</v>
+        <v>281</v>
       </c>
       <c r="F62" s="7">
-        <v>-5.5680287379999998</v>
+        <v>-4.7619047620000003</v>
       </c>
       <c r="G62" s="13" t="s">
-        <v>177</v>
+        <v>142</v>
       </c>
       <c r="H62" s="14">
-        <v>4454</v>
+        <v>295.05</v>
       </c>
       <c r="I62" s="6" t="s">
         <v>8</v>
@@ -3938,30 +3937,30 @@
       <c r="Y62" s="13"/>
       <c r="Z62" s="13"/>
     </row>
-    <row r="63" spans="1:26" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A63" s="5">
-        <v>46244.63559027778</v>
+        <v>46211.635416666664</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D63" s="7">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E63" s="7">
-        <v>1420</v>
+        <v>836</v>
       </c>
       <c r="F63" s="7">
-        <v>-5.534858968</v>
+        <v>-4.8811013770000002</v>
       </c>
       <c r="G63" s="13" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="H63" s="14">
-        <v>1503.2</v>
+        <v>878.9</v>
       </c>
       <c r="I63" s="6" t="s">
         <v>8</v>
@@ -3984,9 +3983,9 @@
       <c r="Y63" s="13"/>
       <c r="Z63" s="13"/>
     </row>
-    <row r="64" spans="1:26" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A64" s="5">
-        <v>46239.696701388886</v>
+        <v>46211.6875</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>21</v>
@@ -3998,10 +3997,10 @@
         <v>100</v>
       </c>
       <c r="E64" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F64" s="7">
-        <v>-5.4740406320000004</v>
+        <v>-4.9097065459999998</v>
       </c>
       <c r="G64" s="13" t="s">
         <v>150</v>
@@ -4030,30 +4029,30 @@
       <c r="Y64" s="13"/>
       <c r="Z64" s="13"/>
     </row>
-    <row r="65" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A65" s="5">
-        <v>46150.635416666664</v>
+        <v>46211.76458333333</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D65" s="7">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E65" s="7">
-        <v>878</v>
+        <v>196</v>
       </c>
       <c r="F65" s="7">
-        <v>-5.4388799140000001</v>
+        <v>-5.0019387359999996</v>
       </c>
       <c r="G65" s="13" t="s">
-        <v>164</v>
+        <v>199</v>
       </c>
       <c r="H65" s="14">
-        <v>928.5</v>
+        <v>206.32</v>
       </c>
       <c r="I65" s="6" t="s">
         <v>8</v>
@@ -4076,30 +4075,30 @@
       <c r="Y65" s="13"/>
       <c r="Z65" s="13"/>
     </row>
-    <row r="66" spans="1:26" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A66" s="15" t="s">
         <v>189</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D66" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E66" s="7">
-        <v>3856</v>
+        <v>852</v>
       </c>
       <c r="F66" s="7">
-        <v>-5.3277682300000002</v>
+        <v>-5.0061322329999998</v>
       </c>
       <c r="G66" s="13" t="s">
-        <v>172</v>
+        <v>143</v>
       </c>
       <c r="H66" s="14">
-        <v>4073</v>
+        <v>896.9</v>
       </c>
       <c r="I66" s="6" t="s">
         <v>8</v>
@@ -4122,30 +4121,30 @@
       <c r="Y66" s="13"/>
       <c r="Z66" s="13"/>
     </row>
-    <row r="67" spans="1:26" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A67" s="5">
-        <v>46244.63554398148</v>
+        <v>46211.6875</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D67" s="7">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="E67" s="7">
-        <v>3410</v>
+        <v>2460</v>
       </c>
       <c r="F67" s="7">
-        <v>-5.1935053379999996</v>
+        <v>-5.1291939839999996</v>
       </c>
       <c r="G67" s="13" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="H67" s="14">
-        <v>3596.8</v>
+        <v>2593</v>
       </c>
       <c r="I67" s="6" t="s">
         <v>8</v>
@@ -4168,30 +4167,30 @@
       <c r="Y67" s="13"/>
       <c r="Z67" s="13"/>
     </row>
-    <row r="68" spans="1:26" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A68" s="5">
-        <v>46211.6875</v>
+        <v>46244.63554398148</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D68" s="7">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="E68" s="7">
-        <v>2460</v>
+        <v>3410</v>
       </c>
       <c r="F68" s="7">
-        <v>-5.1291939839999996</v>
+        <v>-5.1935053379999996</v>
       </c>
       <c r="G68" s="13" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="H68" s="14">
-        <v>2593</v>
+        <v>3596.8</v>
       </c>
       <c r="I68" s="6" t="s">
         <v>8</v>
@@ -4214,30 +4213,30 @@
       <c r="Y68" s="13"/>
       <c r="Z68" s="13"/>
     </row>
-    <row r="69" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A69" s="15" t="s">
         <v>189</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D69" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E69" s="7">
-        <v>852</v>
+        <v>3856</v>
       </c>
       <c r="F69" s="7">
-        <v>-5.0061322329999998</v>
+        <v>-5.3277682300000002</v>
       </c>
       <c r="G69" s="13" t="s">
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="H69" s="14">
-        <v>896.9</v>
+        <v>4073</v>
       </c>
       <c r="I69" s="6" t="s">
         <v>8</v>
@@ -4260,30 +4259,30 @@
       <c r="Y69" s="13"/>
       <c r="Z69" s="13"/>
     </row>
-    <row r="70" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A70" s="5">
-        <v>46211.76458333333</v>
+        <v>46150.635416666664</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>91</v>
+        <v>33</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D70" s="7">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E70" s="7">
-        <v>196</v>
+        <v>878</v>
       </c>
       <c r="F70" s="7">
-        <v>-5.0019387359999996</v>
+        <v>-5.4388799140000001</v>
       </c>
       <c r="G70" s="13" t="s">
-        <v>199</v>
+        <v>164</v>
       </c>
       <c r="H70" s="14">
-        <v>206.32</v>
+        <v>928.5</v>
       </c>
       <c r="I70" s="6" t="s">
         <v>8</v>
@@ -4306,9 +4305,9 @@
       <c r="Y70" s="13"/>
       <c r="Z70" s="13"/>
     </row>
-    <row r="71" spans="1:26" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A71" s="5">
-        <v>46211.6875</v>
+        <v>46239.696701388886</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>21</v>
@@ -4320,10 +4319,10 @@
         <v>100</v>
       </c>
       <c r="E71" s="7">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F71" s="7">
-        <v>-4.9097065459999998</v>
+        <v>-5.4740406320000004</v>
       </c>
       <c r="G71" s="13" t="s">
         <v>150</v>
@@ -4352,30 +4351,30 @@
       <c r="Y71" s="13"/>
       <c r="Z71" s="13"/>
     </row>
-    <row r="72" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:26" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="5">
-        <v>46211.635416666664</v>
+        <v>46244.63559027778</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D72" s="7">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E72" s="7">
-        <v>836</v>
+        <v>1420</v>
       </c>
       <c r="F72" s="7">
-        <v>-4.8811013770000002</v>
+        <v>-5.534858968</v>
       </c>
       <c r="G72" s="13" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H72" s="14">
-        <v>878.9</v>
+        <v>1503.2</v>
       </c>
       <c r="I72" s="6" t="s">
         <v>8</v>
@@ -4398,30 +4397,30 @@
       <c r="Y72" s="13"/>
       <c r="Z72" s="13"/>
     </row>
-    <row r="73" spans="1:26" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="15" t="s">
-        <v>189</v>
+    <row r="73" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A73" s="5">
+        <v>46211.635416666664</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D73" s="7">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E73" s="7">
-        <v>281</v>
+        <v>4206</v>
       </c>
       <c r="F73" s="7">
-        <v>-4.7619047620000003</v>
+        <v>-5.5680287379999998</v>
       </c>
       <c r="G73" s="13" t="s">
-        <v>142</v>
+        <v>177</v>
       </c>
       <c r="H73" s="14">
-        <v>295.05</v>
+        <v>4454</v>
       </c>
       <c r="I73" s="6" t="s">
         <v>8</v>
@@ -4444,30 +4443,30 @@
       <c r="Y73" s="13"/>
       <c r="Z73" s="13"/>
     </row>
-    <row r="74" spans="1:26" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A74" s="5">
-        <v>46240.687962962962</v>
+        <v>46211.76458333333</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D74" s="7">
-        <v>5</v>
+        <v>500</v>
       </c>
       <c r="E74" s="7">
-        <v>2470</v>
+        <v>33.159999999999997</v>
       </c>
       <c r="F74" s="7">
-        <v>-4.7435403010000003</v>
+        <v>-5.5808656040000004</v>
       </c>
       <c r="G74" s="13" t="s">
-        <v>144</v>
+        <v>193</v>
       </c>
       <c r="H74" s="14">
-        <v>2593</v>
+        <v>35.119999999999997</v>
       </c>
       <c r="I74" s="6" t="s">
         <v>8</v>
@@ -4490,12 +4489,12 @@
       <c r="Y74" s="13"/>
       <c r="Z74" s="13"/>
     </row>
-    <row r="75" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A75" s="5">
-        <v>46241.635567129626</v>
+        <v>46240.687962962962</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>10</v>
@@ -4504,16 +4503,16 @@
         <v>5</v>
       </c>
       <c r="E75" s="7">
-        <v>838</v>
+        <v>569</v>
       </c>
       <c r="F75" s="7">
-        <v>-4.653544203</v>
+        <v>-5.8258854680000001</v>
       </c>
       <c r="G75" s="13" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="H75" s="14">
-        <v>878.9</v>
+        <v>604.20000000000005</v>
       </c>
       <c r="I75" s="6" t="s">
         <v>8</v>
@@ -4536,30 +4535,30 @@
       <c r="Y75" s="13"/>
       <c r="Z75" s="13"/>
     </row>
-    <row r="76" spans="1:26" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" s="5">
-        <v>46244.63554398148</v>
+        <v>46244.63553240741</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D76" s="7">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="E76" s="7">
-        <v>1007</v>
+        <v>4640</v>
       </c>
       <c r="F76" s="7">
-        <v>-4.5497630329999996</v>
+        <v>-5.8613483740000003</v>
       </c>
       <c r="G76" s="13" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H76" s="14">
-        <v>1055</v>
+        <v>4928.8999999999996</v>
       </c>
       <c r="I76" s="6" t="s">
         <v>8</v>
@@ -4582,7 +4581,7 @@
       <c r="Y76" s="13"/>
       <c r="Z76" s="13"/>
     </row>
-    <row r="77" spans="1:26" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A77" s="15" t="s">
         <v>189</v>
       </c>
@@ -4593,13 +4592,13 @@
         <v>10</v>
       </c>
       <c r="D77" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E77" s="7">
-        <v>3888</v>
+        <v>3830</v>
       </c>
       <c r="F77" s="7">
-        <v>-4.5421065550000002</v>
+        <v>-5.9661183400000004</v>
       </c>
       <c r="G77" s="13" t="s">
         <v>172</v>
@@ -4628,30 +4627,30 @@
       <c r="Y77" s="13"/>
       <c r="Z77" s="13"/>
     </row>
-    <row r="78" spans="1:26" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A78" s="15" t="s">
-        <v>189</v>
+    <row r="78" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A78" s="5">
+        <v>46211.765277777777</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D78" s="7">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E78" s="7">
-        <v>220.1</v>
+        <v>2435</v>
       </c>
       <c r="F78" s="7">
-        <v>-4.5119305860000001</v>
+        <v>-6.0933281910000003</v>
       </c>
       <c r="G78" s="13" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="H78" s="14">
-        <v>230.5</v>
+        <v>2593</v>
       </c>
       <c r="I78" s="6" t="s">
         <v>8</v>
@@ -4674,30 +4673,30 @@
       <c r="Y78" s="13"/>
       <c r="Z78" s="13"/>
     </row>
-    <row r="79" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A79" s="5">
-        <v>46211.635416666664</v>
+    <row r="79" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A79" s="15" t="s">
+        <v>189</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D79" s="7">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="E79" s="7">
-        <v>1166</v>
+        <v>277</v>
       </c>
       <c r="F79" s="7">
-        <v>-4.5045045049999999</v>
+        <v>-6.1176071849999998</v>
       </c>
       <c r="G79" s="13" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
       <c r="H79" s="14">
-        <v>1221</v>
+        <v>295.05</v>
       </c>
       <c r="I79" s="6" t="s">
         <v>8</v>
@@ -4720,30 +4719,30 @@
       <c r="Y79" s="13"/>
       <c r="Z79" s="13"/>
     </row>
-    <row r="80" spans="1:26" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A80" s="5">
-        <v>46244.63554398148</v>
+        <v>46239.635520833333</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D80" s="7">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E80" s="7">
-        <v>1251</v>
+        <v>1005</v>
       </c>
       <c r="F80" s="7">
-        <v>-4.5038167939999996</v>
+        <v>-6.1624649859999998</v>
       </c>
       <c r="G80" s="13" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="H80" s="14">
-        <v>1310</v>
+        <v>1071</v>
       </c>
       <c r="I80" s="6" t="s">
         <v>8</v>
@@ -4766,30 +4765,30 @@
       <c r="Y80" s="13"/>
       <c r="Z80" s="13"/>
     </row>
-    <row r="81" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A81" s="5">
-        <v>46211.765277777777</v>
+        <v>46181.6875</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D81" s="7">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E81" s="7">
-        <v>190.1</v>
+        <v>1614</v>
       </c>
       <c r="F81" s="7">
-        <v>-4.4819616120000001</v>
+        <v>-6.1627906980000002</v>
       </c>
       <c r="G81" s="13" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H81" s="14">
-        <v>199.02</v>
+        <v>1720</v>
       </c>
       <c r="I81" s="6" t="s">
         <v>8</v>
@@ -4812,30 +4811,30 @@
       <c r="Y81" s="13"/>
       <c r="Z81" s="13"/>
     </row>
-    <row r="82" spans="1:26" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:26" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A82" s="5">
-        <v>46244.767326388886</v>
+        <v>46241.635567129626</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D82" s="7">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E82" s="7">
-        <v>426</v>
+        <v>1410</v>
       </c>
       <c r="F82" s="7">
-        <v>-4.430734717</v>
+        <v>-6.2001064399999999</v>
       </c>
       <c r="G82" s="13" t="s">
-        <v>149</v>
+        <v>176</v>
       </c>
       <c r="H82" s="14">
-        <v>445.75</v>
+        <v>1503.2</v>
       </c>
       <c r="I82" s="6" t="s">
         <v>8</v>
@@ -4858,30 +4857,30 @@
       <c r="Y82" s="13"/>
       <c r="Z82" s="13"/>
     </row>
-    <row r="83" spans="1:26" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A83" s="5">
-        <v>46211.635416666664</v>
+        <v>46241.765462962961</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D83" s="7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E83" s="7">
-        <v>2888</v>
+        <v>2164</v>
       </c>
       <c r="F83" s="7">
-        <v>-4.3708609269999998</v>
+        <v>-6.3203463199999996</v>
       </c>
       <c r="G83" s="13" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="H83" s="14">
-        <v>3020</v>
+        <v>2310</v>
       </c>
       <c r="I83" s="6" t="s">
         <v>8</v>
@@ -4904,30 +4903,30 @@
       <c r="Y83" s="13"/>
       <c r="Z83" s="13"/>
     </row>
-    <row r="84" spans="1:26" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A84" s="5">
-        <v>46244.635509259257</v>
+        <v>46240.687974537039</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D84" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E84" s="7">
-        <v>13552</v>
+        <v>2164</v>
       </c>
       <c r="F84" s="7">
-        <v>-4.3613267469999997</v>
+        <v>-6.3203463199999996</v>
       </c>
       <c r="G84" s="13" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="H84" s="14">
-        <v>14170</v>
+        <v>2310</v>
       </c>
       <c r="I84" s="6" t="s">
         <v>8</v>
@@ -4950,30 +4949,30 @@
       <c r="Y84" s="13"/>
       <c r="Z84" s="13"/>
     </row>
-    <row r="85" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A85" s="5">
-        <v>46244.767418981479</v>
+    <row r="85" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A85" s="15" t="s">
+        <v>189</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D85" s="7">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="E85" s="7">
-        <v>196</v>
+        <v>3810</v>
       </c>
       <c r="F85" s="7">
-        <v>-4.3202343179999998</v>
+        <v>-6.457156887</v>
       </c>
       <c r="G85" s="13" t="s">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="H85" s="14">
-        <v>204.85</v>
+        <v>4073</v>
       </c>
       <c r="I85" s="6" t="s">
         <v>8</v>
@@ -4996,30 +4995,30 @@
       <c r="Y85" s="13"/>
       <c r="Z85" s="13"/>
     </row>
-    <row r="86" spans="1:26" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="5">
-        <v>46244.63559027778</v>
+        <v>46211.635416666664</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D86" s="7">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E86" s="7">
-        <v>1440</v>
+        <v>17552</v>
       </c>
       <c r="F86" s="7">
-        <v>-4.2043640230000001</v>
+        <v>-6.4990411249999998</v>
       </c>
       <c r="G86" s="13" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="H86" s="14">
-        <v>1503.2</v>
+        <v>18772</v>
       </c>
       <c r="I86" s="6" t="s">
         <v>8</v>
@@ -5042,30 +5041,30 @@
       <c r="Y86" s="13"/>
       <c r="Z86" s="13"/>
     </row>
-    <row r="87" spans="1:26" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:26" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A87" s="5">
-        <v>46211.635416666664</v>
+        <v>46211.6875</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D87" s="7">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="E87" s="7">
-        <v>1277</v>
+        <v>206</v>
       </c>
       <c r="F87" s="7">
-        <v>-4.1651031889999999</v>
+        <v>-6.5929083159999999</v>
       </c>
       <c r="G87" s="13" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="H87" s="14">
-        <v>1332.5</v>
+        <v>220.54</v>
       </c>
       <c r="I87" s="6" t="s">
         <v>8</v>
@@ -5088,30 +5087,30 @@
       <c r="Y87" s="13"/>
       <c r="Z87" s="13"/>
     </row>
-    <row r="88" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A88" s="5">
-        <v>46244.767592592594</v>
+    <row r="88" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A88" s="15" t="s">
+        <v>189</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D88" s="7">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="E88" s="7">
-        <v>860</v>
+        <v>331</v>
       </c>
       <c r="F88" s="7">
-        <v>-4.1141710339999999</v>
+        <v>-6.6027088039999997</v>
       </c>
       <c r="G88" s="13" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="H88" s="14">
-        <v>896.9</v>
+        <v>354.4</v>
       </c>
       <c r="I88" s="6" t="s">
         <v>8</v>
@@ -5134,12 +5133,12 @@
       <c r="Y88" s="13"/>
       <c r="Z88" s="13"/>
     </row>
-    <row r="89" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A89" s="5">
-        <v>46244.767326388886</v>
+        <v>46211.765277777777</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>10</v>
@@ -5148,16 +5147,16 @@
         <v>5</v>
       </c>
       <c r="E89" s="7">
-        <v>660</v>
+        <v>452</v>
       </c>
       <c r="F89" s="7">
-        <v>-4.0279191509999999</v>
+        <v>-6.6115702479999996</v>
       </c>
       <c r="G89" s="13" t="s">
-        <v>151</v>
+        <v>190</v>
       </c>
       <c r="H89" s="14">
-        <v>687.7</v>
+        <v>484</v>
       </c>
       <c r="I89" s="6" t="s">
         <v>8</v>
@@ -5180,30 +5179,30 @@
       <c r="Y89" s="13"/>
       <c r="Z89" s="13"/>
     </row>
-    <row r="90" spans="1:26" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A90" s="5">
-        <v>46244.767326388886</v>
+        <v>46244.63554398148</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D90" s="7">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c r="E90" s="7">
-        <v>340.2</v>
+        <v>2401</v>
       </c>
       <c r="F90" s="7">
-        <v>-4.0067720089999996</v>
+        <v>-6.829646876</v>
       </c>
       <c r="G90" s="13" t="s">
-        <v>150</v>
+        <v>182</v>
       </c>
       <c r="H90" s="14">
-        <v>354.4</v>
+        <v>2577</v>
       </c>
       <c r="I90" s="6" t="s">
         <v>8</v>
@@ -5226,30 +5225,30 @@
       <c r="Y90" s="13"/>
       <c r="Z90" s="13"/>
     </row>
-    <row r="91" spans="1:26" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A91" s="5">
-        <v>46211.6875</v>
+        <v>46241.688136574077</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D91" s="7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E91" s="7">
-        <v>2490</v>
+        <v>640</v>
       </c>
       <c r="F91" s="7">
-        <v>-3.9722329350000001</v>
+        <v>-6.9361640250000001</v>
       </c>
       <c r="G91" s="13" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="H91" s="14">
-        <v>2593</v>
+        <v>687.7</v>
       </c>
       <c r="I91" s="6" t="s">
         <v>8</v>
@@ -5272,30 +5271,30 @@
       <c r="Y91" s="13"/>
       <c r="Z91" s="13"/>
     </row>
-    <row r="92" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A92" s="5">
-        <v>46244.767326388886</v>
+        <v>46181.6875</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D92" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E92" s="7">
-        <v>4710</v>
+        <v>640</v>
       </c>
       <c r="F92" s="7">
-        <v>-3.873627495</v>
+        <v>-6.9361640250000001</v>
       </c>
       <c r="G92" s="13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H92" s="14">
-        <v>4899.8</v>
+        <v>687.7</v>
       </c>
       <c r="I92" s="6" t="s">
         <v>8</v>
@@ -5318,30 +5317,30 @@
       <c r="Y92" s="13"/>
       <c r="Z92" s="13"/>
     </row>
-    <row r="93" spans="1:26" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A93" s="5">
-        <v>46244.767326388886</v>
+        <v>46150.793055555558</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D93" s="7">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E93" s="7">
-        <v>212</v>
+        <v>640</v>
       </c>
       <c r="F93" s="7">
-        <v>-3.8723134130000001</v>
+        <v>-6.9361640250000001</v>
       </c>
       <c r="G93" s="13" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H93" s="14">
-        <v>220.54</v>
+        <v>687.7</v>
       </c>
       <c r="I93" s="6" t="s">
         <v>8</v>
@@ -5364,30 +5363,30 @@
       <c r="Y93" s="13"/>
       <c r="Z93" s="13"/>
     </row>
-    <row r="94" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A94" s="5">
-        <v>46244.63553240741</v>
+        <v>46150.793055555558</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D94" s="7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E94" s="7">
-        <v>18052</v>
+        <v>560</v>
       </c>
       <c r="F94" s="7">
-        <v>-3.8354996799999999</v>
+        <v>-7.3154584570000001</v>
       </c>
       <c r="G94" s="13" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="H94" s="14">
-        <v>18772</v>
+        <v>604.20000000000005</v>
       </c>
       <c r="I94" s="6" t="s">
         <v>8</v>
@@ -5410,30 +5409,30 @@
       <c r="Y94" s="13"/>
       <c r="Z94" s="13"/>
     </row>
-    <row r="95" spans="1:26" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A95" s="5">
-        <v>46244.635520833333</v>
+        <v>46240.635567129626</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D95" s="7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E95" s="7">
-        <v>1030</v>
+        <v>2251</v>
       </c>
       <c r="F95" s="7">
-        <v>-3.828197946</v>
+        <v>-7.4195936500000004</v>
       </c>
       <c r="G95" s="13" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H95" s="14">
-        <v>1071</v>
+        <v>2431.4</v>
       </c>
       <c r="I95" s="6" t="s">
         <v>8</v>
@@ -5456,30 +5455,30 @@
       <c r="Y95" s="13"/>
       <c r="Z95" s="13"/>
     </row>
-    <row r="96" spans="1:26" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A96" s="5">
-        <v>46244.63553240741</v>
+        <v>46241.63553240741</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C96" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D96" s="7">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E96" s="7">
-        <v>1260</v>
+        <v>4560</v>
       </c>
       <c r="F96" s="7">
-        <v>-3.8167938929999998</v>
+        <v>-7.4844285739999998</v>
       </c>
       <c r="G96" s="13" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="H96" s="14">
-        <v>1310</v>
+        <v>4928.8999999999996</v>
       </c>
       <c r="I96" s="6" t="s">
         <v>8</v>
@@ -5502,30 +5501,30 @@
       <c r="Y96" s="13"/>
       <c r="Z96" s="13"/>
     </row>
-    <row r="97" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A97" s="5">
-        <v>46240.635578703703</v>
+        <v>46244.767395833333</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D97" s="7">
-        <v>5</v>
+        <v>200</v>
       </c>
       <c r="E97" s="7">
-        <v>1132</v>
+        <v>115.25</v>
       </c>
       <c r="F97" s="7">
-        <v>-3.6595744680000002</v>
+        <v>-7.5262777820000002</v>
       </c>
       <c r="G97" s="13" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="H97" s="14">
-        <v>1175</v>
+        <v>124.63</v>
       </c>
       <c r="I97" s="6" t="s">
         <v>8</v>
@@ -5548,30 +5547,30 @@
       <c r="Y97" s="13"/>
       <c r="Z97" s="13"/>
     </row>
-    <row r="98" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A98" s="5">
-        <v>46241.63553240741</v>
+    <row r="98" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A98" s="15" t="s">
+        <v>189</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="C98" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D98" s="7">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E98" s="7">
-        <v>2460</v>
+        <v>251</v>
       </c>
       <c r="F98" s="7">
-        <v>-3.6427732079999999</v>
+        <v>-7.550644567</v>
       </c>
       <c r="G98" s="13" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="H98" s="14">
-        <v>2553</v>
+        <v>271.5</v>
       </c>
       <c r="I98" s="6" t="s">
         <v>8</v>
@@ -5594,30 +5593,30 @@
       <c r="Y98" s="13"/>
       <c r="Z98" s="13"/>
     </row>
-    <row r="99" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A99" s="5">
-        <v>46244.635520833333</v>
+    <row r="99" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A99" s="15" t="s">
+        <v>189</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D99" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E99" s="7">
-        <v>1066</v>
+        <v>812</v>
       </c>
       <c r="F99" s="7">
-        <v>-3.5294117649999999</v>
+        <v>-7.6117874619999997</v>
       </c>
       <c r="G99" s="13" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="H99" s="14">
-        <v>1105</v>
+        <v>878.9</v>
       </c>
       <c r="I99" s="6" t="s">
         <v>8</v>
@@ -5640,30 +5639,30 @@
       <c r="Y99" s="13"/>
       <c r="Z99" s="13"/>
     </row>
-    <row r="100" spans="1:26" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A100" s="5">
-        <v>46244.63559027778</v>
+    <row r="100" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A100" s="15" t="s">
+        <v>189</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D100" s="7">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E100" s="7">
-        <v>1452</v>
+        <v>3760</v>
       </c>
       <c r="F100" s="7">
-        <v>-3.406067057</v>
+        <v>-7.6847532530000002</v>
       </c>
       <c r="G100" s="13" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="H100" s="14">
-        <v>1503.2</v>
+        <v>4073</v>
       </c>
       <c r="I100" s="6" t="s">
         <v>8</v>
@@ -5686,30 +5685,30 @@
       <c r="Y100" s="13"/>
       <c r="Z100" s="13"/>
     </row>
-    <row r="101" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A101" s="5">
-        <v>46244.635520833333</v>
+    <row r="101" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A101" s="15" t="s">
+        <v>189</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D101" s="7">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="E101" s="7">
-        <v>897</v>
+        <v>4110</v>
       </c>
       <c r="F101" s="7">
-        <v>-3.3925686590000002</v>
+        <v>-7.7233947010000001</v>
       </c>
       <c r="G101" s="13" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="H101" s="14">
-        <v>928.5</v>
+        <v>4454</v>
       </c>
       <c r="I101" s="6" t="s">
         <v>8</v>
@@ -5732,30 +5731,30 @@
       <c r="Y101" s="13"/>
       <c r="Z101" s="13"/>
     </row>
-    <row r="102" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A102" s="15" t="s">
         <v>189</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D102" s="7">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="E102" s="7">
-        <v>702</v>
+        <v>327</v>
       </c>
       <c r="F102" s="7">
-        <v>-3.372333104</v>
+        <v>-7.7313769749999999</v>
       </c>
       <c r="G102" s="13" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="H102" s="14">
-        <v>726.5</v>
+        <v>354.4</v>
       </c>
       <c r="I102" s="6" t="s">
         <v>8</v>
@@ -5778,30 +5777,30 @@
       <c r="Y102" s="13"/>
       <c r="Z102" s="13"/>
     </row>
-    <row r="103" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A103" s="5">
-        <v>46244.63559027778</v>
+        <v>46244.63554398148</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D103" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E103" s="7">
-        <v>4306</v>
+        <v>2560</v>
       </c>
       <c r="F103" s="7">
-        <v>-3.3228558600000002</v>
+        <v>-7.8141879730000001</v>
       </c>
       <c r="G103" s="13" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="H103" s="14">
-        <v>4454</v>
+        <v>2777</v>
       </c>
       <c r="I103" s="6" t="s">
         <v>8</v>
@@ -5824,30 +5823,30 @@
       <c r="Y103" s="13"/>
       <c r="Z103" s="13"/>
     </row>
-    <row r="104" spans="1:26" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A104" s="5">
-        <v>46211.645138888889</v>
+        <v>46211.635416666664</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D104" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E104" s="7">
-        <v>3938</v>
+        <v>3310</v>
       </c>
       <c r="F104" s="7">
-        <v>-3.3145101889999999</v>
+        <v>-7.9737544480000002</v>
       </c>
       <c r="G104" s="13" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="H104" s="14">
-        <v>4073</v>
+        <v>3596.8</v>
       </c>
       <c r="I104" s="6" t="s">
         <v>8</v>
@@ -5870,30 +5869,30 @@
       <c r="Y104" s="13"/>
       <c r="Z104" s="13"/>
     </row>
-    <row r="105" spans="1:26" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A105" s="5">
-        <v>46244.63554398148</v>
+        <v>46244.63553240741</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D105" s="7">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="E105" s="7">
-        <v>390</v>
+        <v>2370</v>
       </c>
       <c r="F105" s="7">
-        <v>-3.3097805880000002</v>
+        <v>-8.0325960419999998</v>
       </c>
       <c r="G105" s="13" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H105" s="14">
-        <v>403.35</v>
+        <v>2577</v>
       </c>
       <c r="I105" s="6" t="s">
         <v>8</v>
@@ -5916,30 +5915,30 @@
       <c r="Y105" s="13"/>
       <c r="Z105" s="13"/>
     </row>
-    <row r="106" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A106" s="5">
-        <v>46244.63559027778</v>
+    <row r="106" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A106" s="15" t="s">
+        <v>189</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D106" s="7">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="E106" s="7">
-        <v>850</v>
+        <v>2552</v>
       </c>
       <c r="F106" s="7">
-        <v>-3.2882011609999999</v>
+        <v>-8.1022686349999997</v>
       </c>
       <c r="G106" s="13" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="H106" s="14">
-        <v>878.9</v>
+        <v>2777</v>
       </c>
       <c r="I106" s="6" t="s">
         <v>8</v>
@@ -5962,30 +5961,30 @@
       <c r="Y106" s="13"/>
       <c r="Z106" s="13"/>
     </row>
-    <row r="107" spans="1:26" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A107" s="5">
-        <v>46244.635555555556</v>
+        <v>46211.765277777777</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D107" s="7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E107" s="7">
-        <v>2352</v>
+        <v>366</v>
       </c>
       <c r="F107" s="7">
-        <v>-3.265608292</v>
+        <v>-8.3854818519999998</v>
       </c>
       <c r="G107" s="13" t="s">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="H107" s="14">
-        <v>2431.4</v>
+        <v>399.5</v>
       </c>
       <c r="I107" s="6" t="s">
         <v>8</v>
@@ -6008,30 +6007,30 @@
       <c r="Y107" s="13"/>
       <c r="Z107" s="13"/>
     </row>
-    <row r="108" spans="1:26" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:26" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A108" s="5">
-        <v>46244.63559027778</v>
+        <v>46240.687974537039</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D108" s="7">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E108" s="7">
-        <v>764</v>
+        <v>202</v>
       </c>
       <c r="F108" s="7">
-        <v>-3.2360205180000001</v>
+        <v>-8.4066382520000005</v>
       </c>
       <c r="G108" s="13" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="H108" s="14">
-        <v>789.55</v>
+        <v>220.54</v>
       </c>
       <c r="I108" s="6" t="s">
         <v>8</v>
@@ -6054,30 +6053,30 @@
       <c r="Y108" s="13"/>
       <c r="Z108" s="13"/>
     </row>
-    <row r="109" spans="1:26" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A109" s="5">
-        <v>46241.765092592592</v>
+        <v>46239.789583333331</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D109" s="7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E109" s="7">
-        <v>2510</v>
+        <v>411</v>
       </c>
       <c r="F109" s="7">
-        <v>-3.2009255689999998</v>
+        <v>-8.46325167</v>
       </c>
       <c r="G109" s="13" t="s">
-        <v>144</v>
+        <v>194</v>
       </c>
       <c r="H109" s="14">
-        <v>2593</v>
+        <v>449</v>
       </c>
       <c r="I109" s="6" t="s">
         <v>8</v>
@@ -6100,30 +6099,30 @@
       <c r="Y109" s="13"/>
       <c r="Z109" s="13"/>
     </row>
-    <row r="110" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A110" s="5">
-        <v>46244.767326388886</v>
+    <row r="110" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A110" s="15" t="s">
+        <v>189</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D110" s="7">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E110" s="7">
-        <v>1666</v>
+        <v>4060</v>
       </c>
       <c r="F110" s="7">
-        <v>-3.1395348840000001</v>
+        <v>-8.8459811409999993</v>
       </c>
       <c r="G110" s="13" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="H110" s="14">
-        <v>1720</v>
+        <v>4454</v>
       </c>
       <c r="I110" s="6" t="s">
         <v>8</v>
@@ -6146,30 +6145,30 @@
       <c r="Y110" s="13"/>
       <c r="Z110" s="13"/>
     </row>
-    <row r="111" spans="1:26" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A111" s="5">
-        <v>46244.767384259256</v>
+    <row r="111" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A111" s="15" t="s">
+        <v>189</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D111" s="7">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="E111" s="7">
-        <v>286</v>
+        <v>322</v>
       </c>
       <c r="F111" s="7">
-        <v>-3.0672767329999999</v>
+        <v>-9.1422121900000004</v>
       </c>
       <c r="G111" s="13" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="H111" s="14">
-        <v>295.05</v>
+        <v>354.4</v>
       </c>
       <c r="I111" s="6" t="s">
         <v>8</v>
@@ -6192,30 +6191,30 @@
       <c r="Y111" s="13"/>
       <c r="Z111" s="13"/>
     </row>
-    <row r="112" spans="1:26" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A112" s="5">
-        <v>46241.645509259259</v>
+        <v>46244.76730324074</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D112" s="7">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E112" s="7">
-        <v>3950</v>
+        <v>547</v>
       </c>
       <c r="F112" s="7">
-        <v>-3.0198870609999999</v>
+        <v>-9.467063886</v>
       </c>
       <c r="G112" s="13" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="H112" s="14">
-        <v>4073</v>
+        <v>604.20000000000005</v>
       </c>
       <c r="I112" s="6" t="s">
         <v>8</v>
@@ -6238,30 +6237,30 @@
       <c r="Y112" s="13"/>
       <c r="Z112" s="13"/>
     </row>
-    <row r="113" spans="1:26" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A113" s="5">
-        <v>46244.767326388886</v>
+        <v>46240.635555555556</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D113" s="7">
-        <v>150</v>
+        <v>2</v>
       </c>
       <c r="E113" s="7">
-        <v>214</v>
+        <v>4456</v>
       </c>
       <c r="F113" s="7">
-        <v>-2.9654484449999998</v>
+        <v>-9.5944328349999992</v>
       </c>
       <c r="G113" s="13" t="s">
-        <v>153</v>
+        <v>184</v>
       </c>
       <c r="H113" s="14">
-        <v>220.54</v>
+        <v>4928.8999999999996</v>
       </c>
       <c r="I113" s="6" t="s">
         <v>8</v>
@@ -6284,30 +6283,30 @@
       <c r="Y113" s="13"/>
       <c r="Z113" s="13"/>
     </row>
-    <row r="114" spans="1:26" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A114" s="5">
-        <v>46181.6875</v>
+    <row r="114" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A114" s="15" t="s">
+        <v>189</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>21</v>
+        <v>73</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D114" s="7">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E114" s="7">
-        <v>344</v>
+        <v>6920</v>
       </c>
       <c r="F114" s="7">
-        <v>-2.9345372460000001</v>
+        <v>-9.8018769549999991</v>
       </c>
       <c r="G114" s="13" t="s">
-        <v>150</v>
+        <v>196</v>
       </c>
       <c r="H114" s="14">
-        <v>354.4</v>
+        <v>7672</v>
       </c>
       <c r="I114" s="6" t="s">
         <v>8</v>
@@ -6330,30 +6329,30 @@
       <c r="Y114" s="13"/>
       <c r="Z114" s="13"/>
     </row>
-    <row r="115" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A115" s="5">
-        <v>46244.645590277774</v>
+        <v>46241.688136574077</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D115" s="7">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E115" s="7">
-        <v>1142</v>
+        <v>620</v>
       </c>
       <c r="F115" s="7">
-        <v>-2.808510638</v>
+        <v>-9.8444088989999994</v>
       </c>
       <c r="G115" s="13" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="H115" s="14">
-        <v>1175</v>
+        <v>687.7</v>
       </c>
       <c r="I115" s="6" t="s">
         <v>8</v>
@@ -6376,30 +6375,30 @@
       <c r="Y115" s="13"/>
       <c r="Z115" s="13"/>
     </row>
-    <row r="116" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A116" s="5">
-        <v>46211.76458333333</v>
+        <v>46240.688055555554</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D116" s="7">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E116" s="7">
-        <v>136.1</v>
+        <v>620</v>
       </c>
       <c r="F116" s="7">
-        <v>-2.7857142860000002</v>
+        <v>-9.8444088989999994</v>
       </c>
       <c r="G116" s="13" t="s">
-        <v>198</v>
+        <v>151</v>
       </c>
       <c r="H116" s="14">
-        <v>140</v>
+        <v>687.7</v>
       </c>
       <c r="I116" s="6" t="s">
         <v>8</v>
@@ -6422,30 +6421,30 @@
       <c r="Y116" s="13"/>
       <c r="Z116" s="13"/>
     </row>
-    <row r="117" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A117" s="5">
-        <v>46181.6875</v>
+    <row r="117" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A117" s="15" t="s">
+        <v>189</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D117" s="7">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="E117" s="7">
-        <v>136.15</v>
+        <v>4010</v>
       </c>
       <c r="F117" s="7">
-        <v>-2.75</v>
+        <v>-9.9685675800000002</v>
       </c>
       <c r="G117" s="13" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="H117" s="14">
-        <v>140</v>
+        <v>4454</v>
       </c>
       <c r="I117" s="6" t="s">
         <v>8</v>
@@ -6468,30 +6467,30 @@
       <c r="Y117" s="13"/>
       <c r="Z117" s="13"/>
     </row>
-    <row r="118" spans="1:26" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:26" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A118" s="5">
-        <v>46244.645601851851</v>
+        <v>46241.765462962961</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D118" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E118" s="7">
-        <v>2938</v>
+        <v>1751</v>
       </c>
       <c r="F118" s="7">
-        <v>-2.7152317880000001</v>
+        <v>-9.9789213920000002</v>
       </c>
       <c r="G118" s="13" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="H118" s="14">
-        <v>3020</v>
+        <v>1945.1</v>
       </c>
       <c r="I118" s="6" t="s">
         <v>8</v>
@@ -6514,30 +6513,30 @@
       <c r="Y118" s="13"/>
       <c r="Z118" s="13"/>
     </row>
-    <row r="119" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A119" s="5">
-        <v>46244.645601851851</v>
+        <v>46241.688090277778</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D119" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E119" s="7">
-        <v>1188</v>
+        <v>4410</v>
       </c>
       <c r="F119" s="7">
-        <v>-2.7027027029999999</v>
+        <v>-9.9963263809999994</v>
       </c>
       <c r="G119" s="13" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H119" s="14">
-        <v>1221</v>
+        <v>4899.8</v>
       </c>
       <c r="I119" s="6" t="s">
         <v>8</v>
@@ -6560,30 +6559,30 @@
       <c r="Y119" s="13"/>
       <c r="Z119" s="13"/>
     </row>
-    <row r="120" spans="1:26" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A120" s="5">
-        <v>46244.645613425928</v>
+        <v>46239.63553240741</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D120" s="7">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E120" s="7">
-        <v>1302</v>
+        <v>4415</v>
       </c>
       <c r="F120" s="7">
-        <v>-2.2889305819999999</v>
+        <v>-10.426261439999999</v>
       </c>
       <c r="G120" s="13" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="H120" s="14">
-        <v>1332.5</v>
+        <v>4928.8999999999996</v>
       </c>
       <c r="I120" s="6" t="s">
         <v>8</v>
@@ -6606,30 +6605,30 @@
       <c r="Y120" s="13"/>
       <c r="Z120" s="13"/>
     </row>
-    <row r="121" spans="1:26" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A121" s="5">
-        <v>46244.76730324074</v>
+    <row r="121" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A121" s="15" t="s">
+        <v>189</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D121" s="7">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="E121" s="7">
-        <v>436</v>
+        <v>2064</v>
       </c>
       <c r="F121" s="7">
-        <v>-2.1873247340000002</v>
+        <v>-10.649350650000001</v>
       </c>
       <c r="G121" s="13" t="s">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="H121" s="14">
-        <v>445.75</v>
+        <v>2310</v>
       </c>
       <c r="I121" s="6" t="s">
         <v>8</v>
@@ -6652,30 +6651,30 @@
       <c r="Y121" s="13"/>
       <c r="Z121" s="13"/>
     </row>
-    <row r="122" spans="1:26" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A122" s="5">
-        <v>46244.76730324074</v>
+    <row r="122" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A122" s="15" t="s">
+        <v>189</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C122" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D122" s="7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E122" s="7">
-        <v>2540</v>
+        <v>4364</v>
       </c>
       <c r="F122" s="7">
-        <v>-2.0439645199999998</v>
+        <v>-10.93514021</v>
       </c>
       <c r="G122" s="13" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="H122" s="14">
-        <v>2593</v>
+        <v>4899.8</v>
       </c>
       <c r="I122" s="6" t="s">
         <v>8</v>
@@ -6698,30 +6697,30 @@
       <c r="Y122" s="13"/>
       <c r="Z122" s="13"/>
     </row>
-    <row r="123" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A123" s="5">
-        <v>46244.645613425928</v>
+        <v>46240.688009259262</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="C123" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D123" s="7">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="E123" s="7">
-        <v>712</v>
+        <v>111</v>
       </c>
       <c r="F123" s="7">
-        <v>-1.9958706129999999</v>
+        <v>-10.936371660000001</v>
       </c>
       <c r="G123" s="13" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="H123" s="14">
-        <v>726.5</v>
+        <v>124.63</v>
       </c>
       <c r="I123" s="6" t="s">
         <v>8</v>
@@ -6744,30 +6743,30 @@
       <c r="Y123" s="13"/>
       <c r="Z123" s="13"/>
     </row>
-    <row r="124" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A124" s="5">
-        <v>46241.765462962961</v>
+    <row r="124" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A124" s="15" t="s">
+        <v>189</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C124" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D124" s="7">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="E124" s="7">
-        <v>2264</v>
+        <v>31.01</v>
       </c>
       <c r="F124" s="7">
-        <v>-1.9913419910000001</v>
+        <v>-11.70273349</v>
       </c>
       <c r="G124" s="13" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H124" s="14">
-        <v>2310</v>
+        <v>35.119999999999997</v>
       </c>
       <c r="I124" s="6" t="s">
         <v>8</v>
@@ -6790,30 +6789,30 @@
       <c r="Y124" s="13"/>
       <c r="Z124" s="13"/>
     </row>
-    <row r="125" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A125" s="5">
-        <v>46244.645590277774</v>
+        <v>46241.765439814815</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="C125" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D125" s="7">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E125" s="7">
-        <v>1152</v>
+        <v>352</v>
       </c>
       <c r="F125" s="7">
-        <v>-1.9574468089999999</v>
+        <v>-11.88986233</v>
       </c>
       <c r="G125" s="13" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="H125" s="14">
-        <v>1175</v>
+        <v>399.5</v>
       </c>
       <c r="I125" s="6" t="s">
         <v>8</v>
@@ -6836,30 +6835,30 @@
       <c r="Y125" s="13"/>
       <c r="Z125" s="13"/>
     </row>
-    <row r="126" spans="1:26" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A126" s="5">
-        <v>46244.76730324074</v>
+        <v>46239.789560185185</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="C126" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D126" s="7">
-        <v>150</v>
+        <v>5</v>
       </c>
       <c r="E126" s="7">
-        <v>128</v>
+        <v>419</v>
       </c>
       <c r="F126" s="7">
-        <v>-1.8931555149999999</v>
+        <v>-13.429752069999999</v>
       </c>
       <c r="G126" s="13" t="s">
-        <v>157</v>
+        <v>190</v>
       </c>
       <c r="H126" s="14">
-        <v>130.47</v>
+        <v>484</v>
       </c>
       <c r="I126" s="6" t="s">
         <v>8</v>
@@ -6882,30 +6881,30 @@
       <c r="Y126" s="13"/>
       <c r="Z126" s="13"/>
     </row>
-    <row r="127" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A127" s="5">
-        <v>46244.767418981479</v>
+    <row r="127" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A127" s="15" t="s">
+        <v>189</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="C127" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D127" s="7">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="E127" s="7">
-        <v>201</v>
+        <v>701</v>
       </c>
       <c r="F127" s="7">
-        <v>-1.8794239690000001</v>
+        <v>-13.72307692</v>
       </c>
       <c r="G127" s="13" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="H127" s="14">
-        <v>204.85</v>
+        <v>812.5</v>
       </c>
       <c r="I127" s="6" t="s">
         <v>8</v>
@@ -6928,30 +6927,30 @@
       <c r="Y127" s="13"/>
       <c r="Z127" s="13"/>
     </row>
-    <row r="128" spans="1:26" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A128" s="5">
-        <v>46244.767326388886</v>
+    <row r="128" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A128" s="15" t="s">
+        <v>189</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C128" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D128" s="7">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E128" s="7">
-        <v>348</v>
+        <v>4164</v>
       </c>
       <c r="F128" s="7">
-        <v>-1.8058690740000001</v>
+        <v>-15.016939470000001</v>
       </c>
       <c r="G128" s="13" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H128" s="14">
-        <v>354.4</v>
+        <v>4899.8</v>
       </c>
       <c r="I128" s="6" t="s">
         <v>8</v>
@@ -6974,30 +6973,30 @@
       <c r="Y128" s="13"/>
       <c r="Z128" s="13"/>
     </row>
-    <row r="129" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A129" s="5">
-        <v>46244.767592592594</v>
+        <v>46239.789560185185</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="C129" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D129" s="7">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E129" s="7">
-        <v>882</v>
+        <v>336</v>
       </c>
       <c r="F129" s="7">
-        <v>-1.661277734</v>
+        <v>-15.89486859</v>
       </c>
       <c r="G129" s="13" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="H129" s="14">
-        <v>896.9</v>
+        <v>399.5</v>
       </c>
       <c r="I129" s="6" t="s">
         <v>8</v>
@@ -7020,30 +7019,30 @@
       <c r="Y129" s="13"/>
       <c r="Z129" s="13"/>
     </row>
-    <row r="130" spans="1:26" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A130" s="5">
-        <v>46244.76730324074</v>
+    <row r="130" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A130" s="15" t="s">
+        <v>189</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="C130" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D130" s="7">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="E130" s="7">
-        <v>2552</v>
+        <v>401</v>
       </c>
       <c r="F130" s="7">
-        <v>-1.5811801000000001</v>
+        <v>-17.148760330000002</v>
       </c>
       <c r="G130" s="13" t="s">
-        <v>144</v>
+        <v>190</v>
       </c>
       <c r="H130" s="14">
-        <v>2593</v>
+        <v>484</v>
       </c>
       <c r="I130" s="6" t="s">
         <v>8</v>
@@ -7066,30 +7065,30 @@
       <c r="Y130" s="13"/>
       <c r="Z130" s="13"/>
     </row>
-    <row r="131" spans="1:26" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A131" s="5">
-        <v>46244.645648148151</v>
+    <row r="131" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A131" s="15" t="s">
+        <v>189</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="C131" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D131" s="7">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="E131" s="7">
-        <v>87.3</v>
+        <v>4014</v>
       </c>
       <c r="F131" s="7">
-        <v>-1.322482197</v>
+        <v>-18.078288910000001</v>
       </c>
       <c r="G131" s="13" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="H131" s="14">
-        <v>88.47</v>
+        <v>4899.8</v>
       </c>
       <c r="I131" s="6" t="s">
         <v>8</v>
@@ -7112,30 +7111,30 @@
       <c r="Y131" s="13"/>
       <c r="Z131" s="13"/>
     </row>
-    <row r="132" spans="1:26" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:26" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A132" s="5">
-        <v>46244.645636574074</v>
+        <v>46244.767407407409</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="C132" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D132" s="7">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="E132" s="7">
-        <v>227.5</v>
+        <v>660</v>
       </c>
       <c r="F132" s="7">
-        <v>-1.301518438</v>
+        <v>-19.805589309999998</v>
       </c>
       <c r="G132" s="13" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="H132" s="14">
-        <v>230.5</v>
+        <v>823</v>
       </c>
       <c r="I132" s="6" t="s">
         <v>8</v>
@@ -7158,30 +7157,30 @@
       <c r="Y132" s="13"/>
       <c r="Z132" s="13"/>
     </row>
-    <row r="133" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A133" s="5">
-        <v>46244.645636574074</v>
+    <row r="133" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A133" s="15" t="s">
+        <v>189</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="C133" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D133" s="7">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E133" s="7">
-        <v>917</v>
+        <v>3914</v>
       </c>
       <c r="F133" s="7">
-        <v>-1.2385568119999999</v>
+        <v>-20.11918854</v>
       </c>
       <c r="G133" s="13" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="H133" s="14">
-        <v>928.5</v>
+        <v>4899.8</v>
       </c>
       <c r="I133" s="6" t="s">
         <v>8</v>
@@ -7204,30 +7203,30 @@
       <c r="Y133" s="13"/>
       <c r="Z133" s="13"/>
     </row>
-    <row r="134" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A134" s="5">
-        <v>46239.635555555556</v>
+        <v>46244.767430555556</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="C134" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D134" s="7">
         <v>10</v>
       </c>
-      <c r="D134" s="7">
-        <v>5</v>
-      </c>
       <c r="E134" s="7">
-        <v>1161</v>
+        <v>2604</v>
       </c>
       <c r="F134" s="7">
-        <v>-1.191489362</v>
+        <v>0.42421905129999998</v>
       </c>
       <c r="G134" s="13" t="s">
-        <v>173</v>
+        <v>144</v>
       </c>
       <c r="H134" s="14">
-        <v>1175</v>
+        <v>2593</v>
       </c>
       <c r="I134" s="6" t="s">
         <v>8</v>
@@ -7250,30 +7249,30 @@
       <c r="Y134" s="13"/>
       <c r="Z134" s="13"/>
     </row>
-    <row r="135" spans="1:26" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A135" s="5">
         <v>46244.645601851851</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C135" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D135" s="7">
         <v>10</v>
       </c>
-      <c r="D135" s="7">
-        <v>5</v>
-      </c>
       <c r="E135" s="7">
-        <v>1162</v>
+        <v>1320</v>
       </c>
       <c r="F135" s="7">
-        <v>-1.1063829789999999</v>
+        <v>0.76335877860000001</v>
       </c>
       <c r="G135" s="13" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H135" s="14">
-        <v>1175</v>
+        <v>1310</v>
       </c>
       <c r="I135" s="6" t="s">
         <v>8</v>
@@ -7296,30 +7295,30 @@
       <c r="Y135" s="13"/>
       <c r="Z135" s="13"/>
     </row>
-    <row r="136" spans="1:26" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A136" s="5">
-        <v>46240.645104166666</v>
+        <v>46244.645613425928</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D136" s="7">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="E136" s="7">
-        <v>229</v>
+        <v>3633</v>
       </c>
       <c r="F136" s="7">
-        <v>-0.65075921910000001</v>
+        <v>1.0064501779999999</v>
       </c>
       <c r="G136" s="13" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H136" s="14">
-        <v>230.5</v>
+        <v>3596.8</v>
       </c>
       <c r="I136" s="6" t="s">
         <v>8</v>
@@ -7342,30 +7341,30 @@
       <c r="Y136" s="13"/>
       <c r="Z136" s="13"/>
     </row>
-    <row r="137" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A137" s="5">
-        <v>46244.767430555556</v>
+        <v>46244.645601851851</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="C137" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D137" s="7">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E137" s="7">
-        <v>2604</v>
+        <v>4129</v>
       </c>
       <c r="F137" s="7">
-        <v>0.42421905129999998</v>
+        <v>1.37490793</v>
       </c>
       <c r="G137" s="13" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="H137" s="14">
-        <v>2593</v>
+        <v>4073</v>
       </c>
       <c r="I137" s="6" t="s">
         <v>8</v>
@@ -7388,30 +7387,30 @@
       <c r="Y137" s="13"/>
       <c r="Z137" s="13"/>
     </row>
-    <row r="138" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A138" s="5">
-        <v>46244.645601851851</v>
+        <v>46244.767407407409</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="C138" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D138" s="7">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E138" s="7">
-        <v>1320</v>
+        <v>296</v>
       </c>
       <c r="F138" s="7">
-        <v>0.76335877860000001</v>
+        <v>1.5089163240000001</v>
       </c>
       <c r="G138" s="13" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="H138" s="14">
-        <v>1310</v>
+        <v>291.60000000000002</v>
       </c>
       <c r="I138" s="6" t="s">
         <v>8</v>
@@ -7434,30 +7433,30 @@
       <c r="Y138" s="13"/>
       <c r="Z138" s="13"/>
     </row>
-    <row r="139" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A139" s="5">
-        <v>46244.645613425928</v>
+        <v>46244.645648148151</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="C139" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D139" s="7">
-        <v>5</v>
+        <v>200</v>
       </c>
       <c r="E139" s="7">
-        <v>3633</v>
+        <v>234</v>
       </c>
       <c r="F139" s="7">
-        <v>1.0064501779999999</v>
+        <v>1.518438178</v>
       </c>
       <c r="G139" s="13" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H139" s="14">
-        <v>3596.8</v>
+        <v>230.5</v>
       </c>
       <c r="I139" s="6" t="s">
         <v>8</v>
@@ -7480,30 +7479,30 @@
       <c r="Y139" s="13"/>
       <c r="Z139" s="13"/>
     </row>
-    <row r="140" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A140" s="5">
-        <v>46244.645601851851</v>
+        <v>46244.76730324074</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="C140" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D140" s="7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E140" s="7">
-        <v>4129</v>
+        <v>2636</v>
       </c>
       <c r="F140" s="7">
-        <v>1.37490793</v>
+        <v>1.6583108369999999</v>
       </c>
       <c r="G140" s="13" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="H140" s="14">
-        <v>4073</v>
+        <v>2593</v>
       </c>
       <c r="I140" s="6" t="s">
         <v>8</v>
@@ -7526,12 +7525,12 @@
       <c r="Y140" s="13"/>
       <c r="Z140" s="13"/>
     </row>
-    <row r="141" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A141" s="5">
-        <v>46244.767407407409</v>
+        <v>46244.76730324074</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C141" s="6" t="s">
         <v>7</v>
@@ -7540,16 +7539,16 @@
         <v>50</v>
       </c>
       <c r="E141" s="7">
-        <v>296</v>
+        <v>361</v>
       </c>
       <c r="F141" s="7">
-        <v>1.5089163240000001</v>
+        <v>1.8623024829999999</v>
       </c>
       <c r="G141" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="H141" s="14">
-        <v>291.60000000000002</v>
+        <v>354.4</v>
       </c>
       <c r="I141" s="6" t="s">
         <v>8</v>
@@ -7572,30 +7571,30 @@
       <c r="Y141" s="13"/>
       <c r="Z141" s="13"/>
     </row>
-    <row r="142" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A142" s="5">
-        <v>46244.645648148151</v>
+        <v>46244.645601851851</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C142" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D142" s="7">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="E142" s="7">
-        <v>234</v>
+        <v>896</v>
       </c>
       <c r="F142" s="7">
-        <v>1.518438178</v>
+        <v>1.9456138350000001</v>
       </c>
       <c r="G142" s="13" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="H142" s="14">
-        <v>230.5</v>
+        <v>878.9</v>
       </c>
       <c r="I142" s="6" t="s">
         <v>8</v>
@@ -7632,10 +7631,10 @@
         <v>10</v>
       </c>
       <c r="E143" s="7">
-        <v>2636</v>
+        <v>2648</v>
       </c>
       <c r="F143" s="7">
-        <v>1.6583108369999999</v>
+        <v>2.1210952559999998</v>
       </c>
       <c r="G143" s="13" t="s">
         <v>144</v>
@@ -7664,30 +7663,30 @@
       <c r="Y143" s="13"/>
       <c r="Z143" s="13"/>
     </row>
-    <row r="144" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A144" s="5">
-        <v>46244.76730324074</v>
+        <v>46244.645624999997</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="C144" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D144" s="7">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E144" s="7">
-        <v>361</v>
+        <v>19198</v>
       </c>
       <c r="F144" s="7">
-        <v>1.8623024829999999</v>
+        <v>2.2693373110000001</v>
       </c>
       <c r="G144" s="13" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="H144" s="14">
-        <v>354.4</v>
+        <v>18772</v>
       </c>
       <c r="I144" s="6" t="s">
         <v>8</v>
@@ -7712,28 +7711,28 @@
     </row>
     <row r="145" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A145" s="5">
-        <v>46244.645601851851</v>
+        <v>46244.767418981479</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="C145" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D145" s="7">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E145" s="7">
-        <v>896</v>
+        <v>209.5</v>
       </c>
       <c r="F145" s="7">
-        <v>1.9456138350000001</v>
+        <v>2.2699536249999999</v>
       </c>
       <c r="G145" s="13" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="H145" s="14">
-        <v>878.9</v>
+        <v>204.85</v>
       </c>
       <c r="I145" s="6" t="s">
         <v>8</v>
@@ -7758,28 +7757,28 @@
     </row>
     <row r="146" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A146" s="5">
-        <v>46244.76730324074</v>
+        <v>46244.645671296297</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C146" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D146" s="7">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E146" s="7">
-        <v>2648</v>
+        <v>2846</v>
       </c>
       <c r="F146" s="7">
-        <v>2.1210952559999998</v>
+        <v>2.484695715</v>
       </c>
       <c r="G146" s="13" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="H146" s="14">
-        <v>2593</v>
+        <v>2777</v>
       </c>
       <c r="I146" s="6" t="s">
         <v>8</v>
@@ -7802,30 +7801,30 @@
       <c r="Y146" s="13"/>
       <c r="Z146" s="13"/>
     </row>
-    <row r="147" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A147" s="5">
-        <v>46244.645624999997</v>
+        <v>46244.645601851851</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C147" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D147" s="7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E147" s="7">
-        <v>19198</v>
+        <v>4177</v>
       </c>
       <c r="F147" s="7">
-        <v>2.2693373110000001</v>
+        <v>2.553400442</v>
       </c>
       <c r="G147" s="13" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="H147" s="14">
-        <v>18772</v>
+        <v>4073</v>
       </c>
       <c r="I147" s="6" t="s">
         <v>8</v>
@@ -7848,30 +7847,30 @@
       <c r="Y147" s="13"/>
       <c r="Z147" s="13"/>
     </row>
-    <row r="148" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A148" s="5">
-        <v>46244.767418981479</v>
+        <v>46244.645613425928</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="C148" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D148" s="7">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="E148" s="7">
-        <v>209.5</v>
+        <v>90.75</v>
       </c>
       <c r="F148" s="7">
-        <v>2.2699536249999999</v>
+        <v>2.5771447950000002</v>
       </c>
       <c r="G148" s="13" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="H148" s="14">
-        <v>204.85</v>
+        <v>88.47</v>
       </c>
       <c r="I148" s="6" t="s">
         <v>8</v>
@@ -7896,28 +7895,28 @@
     </row>
     <row r="149" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A149" s="5">
-        <v>46244.645671296297</v>
+        <v>46244.645682870374</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="C149" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D149" s="7">
-        <v>3</v>
+        <v>150</v>
       </c>
       <c r="E149" s="7">
-        <v>2846</v>
+        <v>123.4</v>
       </c>
       <c r="F149" s="7">
-        <v>2.484695715</v>
+        <v>2.8333333330000001</v>
       </c>
       <c r="G149" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H149" s="14">
-        <v>2777</v>
+        <v>120</v>
       </c>
       <c r="I149" s="6" t="s">
         <v>8</v>
@@ -7945,25 +7944,25 @@
         <v>46244.645601851851</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C150" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D150" s="7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E150" s="7">
-        <v>4177</v>
+        <v>1348</v>
       </c>
       <c r="F150" s="7">
-        <v>2.553400442</v>
+        <v>2.9007633589999999</v>
       </c>
       <c r="G150" s="13" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H150" s="14">
-        <v>4073</v>
+        <v>1310</v>
       </c>
       <c r="I150" s="6" t="s">
         <v>8</v>
@@ -7986,30 +7985,30 @@
       <c r="Y150" s="13"/>
       <c r="Z150" s="13"/>
     </row>
-    <row r="151" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:26" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A151" s="5">
-        <v>46244.645613425928</v>
+        <v>46244.63559027778</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C151" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D151" s="7">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="E151" s="7">
-        <v>90.75</v>
+        <v>1548</v>
       </c>
       <c r="F151" s="7">
-        <v>2.5771447950000002</v>
+        <v>2.9803086749999999</v>
       </c>
       <c r="G151" s="13" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="H151" s="14">
-        <v>88.47</v>
+        <v>1503.2</v>
       </c>
       <c r="I151" s="6" t="s">
         <v>8</v>
@@ -8032,30 +8031,30 @@
       <c r="Y151" s="13"/>
       <c r="Z151" s="13"/>
     </row>
-    <row r="152" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A152" s="5">
-        <v>46244.645682870374</v>
+        <v>46244.76730324074</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="C152" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D152" s="7">
+        <v>50</v>
+      </c>
+      <c r="E152" s="7">
+        <v>365</v>
+      </c>
+      <c r="F152" s="7">
+        <v>2.9909706549999999</v>
+      </c>
+      <c r="G152" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="E152" s="7">
-        <v>123.4</v>
-      </c>
-      <c r="F152" s="7">
-        <v>2.8333333330000001</v>
-      </c>
-      <c r="G152" s="13" t="s">
-        <v>160</v>
-      </c>
       <c r="H152" s="14">
-        <v>120</v>
+        <v>354.4</v>
       </c>
       <c r="I152" s="6" t="s">
         <v>8</v>
@@ -8078,12 +8077,12 @@
       <c r="Y152" s="13"/>
       <c r="Z152" s="13"/>
     </row>
-    <row r="153" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A153" s="5">
-        <v>46244.645601851851</v>
+        <v>46244.76730324074</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="C153" s="6" t="s">
         <v>7</v>
@@ -8092,16 +8091,16 @@
         <v>10</v>
       </c>
       <c r="E153" s="7">
-        <v>1348</v>
+        <v>2672</v>
       </c>
       <c r="F153" s="7">
-        <v>2.9007633589999999</v>
+        <v>3.0466640960000002</v>
       </c>
       <c r="G153" s="13" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="H153" s="14">
-        <v>1310</v>
+        <v>2593</v>
       </c>
       <c r="I153" s="6" t="s">
         <v>8</v>
@@ -8124,30 +8123,30 @@
       <c r="Y153" s="13"/>
       <c r="Z153" s="13"/>
     </row>
-    <row r="154" spans="1:26" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A154" s="5">
-        <v>46244.63559027778</v>
+        <v>46244.76730324074</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="C154" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D154" s="7">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="E154" s="7">
-        <v>1548</v>
+        <v>300.5</v>
       </c>
       <c r="F154" s="7">
-        <v>2.9803086749999999</v>
+        <v>3.0521262</v>
       </c>
       <c r="G154" s="13" t="s">
-        <v>176</v>
+        <v>147</v>
       </c>
       <c r="H154" s="14">
-        <v>1503.2</v>
+        <v>291.60000000000002</v>
       </c>
       <c r="I154" s="6" t="s">
         <v>8</v>
@@ -8170,30 +8169,30 @@
       <c r="Y154" s="13"/>
       <c r="Z154" s="13"/>
     </row>
-    <row r="155" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A155" s="5">
-        <v>46244.76730324074</v>
+        <v>46244.645601851851</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="C155" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D155" s="7">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="E155" s="7">
-        <v>365</v>
+        <v>957</v>
       </c>
       <c r="F155" s="7">
-        <v>2.9909706549999999</v>
+        <v>3.069466882</v>
       </c>
       <c r="G155" s="13" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="H155" s="14">
-        <v>354.4</v>
+        <v>928.5</v>
       </c>
       <c r="I155" s="6" t="s">
         <v>8</v>
@@ -8216,30 +8215,30 @@
       <c r="Y155" s="13"/>
       <c r="Z155" s="13"/>
     </row>
-    <row r="156" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A156" s="5">
-        <v>46244.76730324074</v>
+        <v>46241.635555555556</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="C156" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D156" s="7">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E156" s="7">
-        <v>2672</v>
+        <v>3710</v>
       </c>
       <c r="F156" s="7">
-        <v>3.0466640960000002</v>
+        <v>3.1472419930000002</v>
       </c>
       <c r="G156" s="13" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="H156" s="14">
-        <v>2593</v>
+        <v>3596.8</v>
       </c>
       <c r="I156" s="6" t="s">
         <v>8</v>
@@ -8262,30 +8261,30 @@
       <c r="Y156" s="13"/>
       <c r="Z156" s="13"/>
     </row>
-    <row r="157" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:26" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A157" s="5">
         <v>46244.76730324074</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C157" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D157" s="7">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="E157" s="7">
-        <v>300.5</v>
+        <v>940</v>
       </c>
       <c r="F157" s="7">
-        <v>3.0521262</v>
+        <v>3.1833150379999999</v>
       </c>
       <c r="G157" s="13" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="H157" s="14">
-        <v>291.60000000000002</v>
+        <v>911</v>
       </c>
       <c r="I157" s="6" t="s">
         <v>8</v>
@@ -8308,30 +8307,30 @@
       <c r="Y157" s="13"/>
       <c r="Z157" s="13"/>
     </row>
-    <row r="158" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A158" s="5">
-        <v>46244.645601851851</v>
+    <row r="158" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A158" s="15" t="s">
+        <v>189</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C158" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D158" s="7">
-        <v>10</v>
-      </c>
-      <c r="E158" s="7">
-        <v>957</v>
+        <v>150</v>
+      </c>
+      <c r="E158" s="8">
+        <v>134.80000000000001</v>
       </c>
       <c r="F158" s="7">
-        <v>3.069466882</v>
+        <v>3.318770599</v>
       </c>
       <c r="G158" s="13" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="H158" s="14">
-        <v>928.5</v>
+        <v>130.47</v>
       </c>
       <c r="I158" s="6" t="s">
         <v>8</v>
@@ -8354,30 +8353,30 @@
       <c r="Y158" s="13"/>
       <c r="Z158" s="13"/>
     </row>
-    <row r="159" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A159" s="5">
-        <v>46241.635555555556</v>
+        <v>46244.635520833333</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="C159" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D159" s="7">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E159" s="7">
-        <v>3710</v>
+        <v>238.2</v>
       </c>
       <c r="F159" s="7">
-        <v>3.1472419930000002</v>
+        <v>3.3405639909999998</v>
       </c>
       <c r="G159" s="13" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H159" s="14">
-        <v>3596.8</v>
+        <v>230.5</v>
       </c>
       <c r="I159" s="6" t="s">
         <v>8</v>
@@ -8400,30 +8399,30 @@
       <c r="Y159" s="13"/>
       <c r="Z159" s="13"/>
     </row>
-    <row r="160" spans="1:26" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A160" s="5">
-        <v>46244.76730324074</v>
+        <v>46244.635520833333</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C160" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D160" s="7">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="E160" s="7">
-        <v>940</v>
+        <v>239</v>
       </c>
       <c r="F160" s="7">
-        <v>3.1833150379999999</v>
+        <v>3.6876355749999998</v>
       </c>
       <c r="G160" s="13" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H160" s="14">
-        <v>911</v>
+        <v>230.5</v>
       </c>
       <c r="I160" s="6" t="s">
         <v>8</v>
@@ -8447,29 +8446,29 @@
       <c r="Z160" s="13"/>
     </row>
     <row r="161" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A161" s="15" t="s">
-        <v>189</v>
+      <c r="A161" s="5">
+        <v>46244.635601851849</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="C161" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D161" s="7">
-        <v>150</v>
-      </c>
-      <c r="E161" s="8">
-        <v>134.80000000000001</v>
+        <v>200</v>
+      </c>
+      <c r="E161" s="7">
+        <v>91.75</v>
       </c>
       <c r="F161" s="7">
-        <v>3.318770599</v>
+        <v>3.7074714590000002</v>
       </c>
       <c r="G161" s="13" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="H161" s="14">
-        <v>130.47</v>
+        <v>88.47</v>
       </c>
       <c r="I161" s="6" t="s">
         <v>8</v>
@@ -8492,30 +8491,30 @@
       <c r="Y161" s="13"/>
       <c r="Z161" s="13"/>
     </row>
-    <row r="162" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A162" s="5">
-        <v>46244.635520833333</v>
+        <v>46181.635416666664</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C162" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D162" s="7">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="E162" s="7">
-        <v>238.2</v>
+        <v>1360</v>
       </c>
       <c r="F162" s="7">
-        <v>3.3405639909999998</v>
+        <v>3.8167938929999998</v>
       </c>
       <c r="G162" s="13" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="H162" s="14">
-        <v>230.5</v>
+        <v>1310</v>
       </c>
       <c r="I162" s="6" t="s">
         <v>8</v>
@@ -8538,30 +8537,30 @@
       <c r="Y162" s="13"/>
       <c r="Z162" s="13"/>
     </row>
-    <row r="163" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A163" s="5">
-        <v>46244.635520833333</v>
+        <v>46244.63554398148</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C163" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D163" s="7">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="E163" s="7">
-        <v>239</v>
+        <v>1221</v>
       </c>
       <c r="F163" s="7">
-        <v>3.6876355749999998</v>
+        <v>3.9148936170000002</v>
       </c>
       <c r="G163" s="13" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="H163" s="14">
-        <v>230.5</v>
+        <v>1175</v>
       </c>
       <c r="I163" s="6" t="s">
         <v>8</v>
@@ -8586,28 +8585,28 @@
     </row>
     <row r="164" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A164" s="5">
-        <v>46244.635601851849</v>
+        <v>46244.76730324074</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="C164" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D164" s="7">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="E164" s="7">
-        <v>91.75</v>
+        <v>2696</v>
       </c>
       <c r="F164" s="7">
-        <v>3.7074714590000002</v>
+        <v>3.9722329350000001</v>
       </c>
       <c r="G164" s="13" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="H164" s="14">
-        <v>88.47</v>
+        <v>2593</v>
       </c>
       <c r="I164" s="6" t="s">
         <v>8</v>
@@ -8630,30 +8629,30 @@
       <c r="Y164" s="13"/>
       <c r="Z164" s="13"/>
     </row>
-    <row r="165" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A165" s="5">
-        <v>46181.635416666664</v>
+        <v>46239.635578703703</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="C165" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D165" s="7">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="E165" s="7">
-        <v>1360</v>
+        <v>124.9</v>
       </c>
       <c r="F165" s="7">
-        <v>3.8167938929999998</v>
+        <v>4.0833333329999997</v>
       </c>
       <c r="G165" s="13" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="H165" s="14">
-        <v>1310</v>
+        <v>120</v>
       </c>
       <c r="I165" s="6" t="s">
         <v>8</v>
@@ -8676,30 +8675,30 @@
       <c r="Y165" s="13"/>
       <c r="Z165" s="13"/>
     </row>
-    <row r="166" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A166" s="5">
-        <v>46244.63554398148</v>
+        <v>46244.76730324074</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="C166" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D166" s="7">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="E166" s="7">
-        <v>1221</v>
+        <v>369</v>
       </c>
       <c r="F166" s="7">
-        <v>3.9148936170000002</v>
+        <v>4.1196388260000001</v>
       </c>
       <c r="G166" s="13" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="H166" s="14">
-        <v>1175</v>
+        <v>354.4</v>
       </c>
       <c r="I166" s="6" t="s">
         <v>8</v>
@@ -8727,25 +8726,25 @@
         <v>46244.76730324074</v>
       </c>
       <c r="B167" s="6" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C167" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D167" s="7">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="E167" s="7">
-        <v>2696</v>
+        <v>136</v>
       </c>
       <c r="F167" s="7">
-        <v>3.9722329350000001</v>
+        <v>4.2385222660000004</v>
       </c>
       <c r="G167" s="13" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="H167" s="14">
-        <v>2593</v>
+        <v>130.47</v>
       </c>
       <c r="I167" s="6" t="s">
         <v>8</v>
@@ -8768,30 +8767,30 @@
       <c r="Y167" s="13"/>
       <c r="Z167" s="13"/>
     </row>
-    <row r="168" spans="1:26" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A168" s="5">
-        <v>46240.688078703701</v>
+        <v>46244.76730324074</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C168" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D168" s="7">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E168" s="7">
-        <v>948</v>
+        <v>214</v>
       </c>
       <c r="F168" s="7">
-        <v>4.0614709109999998</v>
+        <v>4.466682939</v>
       </c>
       <c r="G168" s="13" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="H168" s="14">
-        <v>911</v>
+        <v>204.85</v>
       </c>
       <c r="I168" s="6" t="s">
         <v>8</v>
@@ -8816,28 +8815,28 @@
     </row>
     <row r="169" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A169" s="5">
-        <v>46239.635578703703</v>
+        <v>46244.635578703703</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C169" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D169" s="7">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="E169" s="7">
-        <v>124.9</v>
+        <v>825</v>
       </c>
       <c r="F169" s="7">
-        <v>4.0833333329999997</v>
+        <v>4.4898993100000002</v>
       </c>
       <c r="G169" s="13" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="H169" s="14">
-        <v>120</v>
+        <v>789.55</v>
       </c>
       <c r="I169" s="6" t="s">
         <v>8</v>
@@ -8860,30 +8859,30 @@
       <c r="Y169" s="13"/>
       <c r="Z169" s="13"/>
     </row>
-    <row r="170" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:26" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A170" s="5">
         <v>46244.76730324074</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C170" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D170" s="7">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="E170" s="7">
-        <v>369</v>
+        <v>467.25</v>
       </c>
       <c r="F170" s="7">
-        <v>4.1196388260000001</v>
+        <v>4.8233314639999998</v>
       </c>
       <c r="G170" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H170" s="14">
-        <v>354.4</v>
+        <v>445.75</v>
       </c>
       <c r="I170" s="6" t="s">
         <v>8</v>
@@ -8908,28 +8907,28 @@
     </row>
     <row r="171" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A171" s="5">
-        <v>46244.76730324074</v>
+        <v>46241.635578703703</v>
       </c>
       <c r="B171" s="6" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="C171" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D171" s="7">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="E171" s="7">
-        <v>136</v>
+        <v>92.75</v>
       </c>
       <c r="F171" s="7">
-        <v>4.2385222660000004</v>
+        <v>4.8377981239999999</v>
       </c>
       <c r="G171" s="13" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="H171" s="14">
-        <v>130.47</v>
+        <v>88.47</v>
       </c>
       <c r="I171" s="6" t="s">
         <v>8</v>
@@ -8952,30 +8951,30 @@
       <c r="Y171" s="13"/>
       <c r="Z171" s="13"/>
     </row>
-    <row r="172" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A172" s="5">
-        <v>46244.76730324074</v>
+        <v>46241.688055555554</v>
       </c>
       <c r="B172" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C172" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D172" s="7">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="E172" s="7">
-        <v>214</v>
+        <v>2720</v>
       </c>
       <c r="F172" s="7">
-        <v>4.466682939</v>
+        <v>4.8978017740000004</v>
       </c>
       <c r="G172" s="13" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H172" s="14">
-        <v>204.85</v>
+        <v>2593</v>
       </c>
       <c r="I172" s="6" t="s">
         <v>8</v>
@@ -9000,28 +8999,28 @@
     </row>
     <row r="173" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A173" s="5">
-        <v>46244.635578703703</v>
+        <v>46241.635567129626</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="C173" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D173" s="7">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="E173" s="7">
-        <v>825</v>
+        <v>125.9</v>
       </c>
       <c r="F173" s="7">
-        <v>4.4898993100000002</v>
+        <v>4.9166666670000003</v>
       </c>
       <c r="G173" s="13" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="H173" s="14">
-        <v>789.55</v>
+        <v>120</v>
       </c>
       <c r="I173" s="6" t="s">
         <v>8</v>
@@ -9044,30 +9043,30 @@
       <c r="Y173" s="13"/>
       <c r="Z173" s="13"/>
     </row>
-    <row r="174" spans="1:26" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A174" s="5">
-        <v>46244.76730324074</v>
+        <v>46244.63553240741</v>
       </c>
       <c r="B174" s="6" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="C174" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D174" s="7">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E174" s="7">
-        <v>467.25</v>
+        <v>424</v>
       </c>
       <c r="F174" s="7">
-        <v>4.8233314639999998</v>
+        <v>5.1196231560000003</v>
       </c>
       <c r="G174" s="13" t="s">
-        <v>149</v>
+        <v>180</v>
       </c>
       <c r="H174" s="14">
-        <v>445.75</v>
+        <v>403.35</v>
       </c>
       <c r="I174" s="6" t="s">
         <v>8</v>
@@ -9090,30 +9089,30 @@
       <c r="Y174" s="13"/>
       <c r="Z174" s="13"/>
     </row>
-    <row r="175" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A175" s="5">
-        <v>46241.635578703703</v>
+        <v>46241.765462962961</v>
       </c>
       <c r="B175" s="6" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="C175" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D175" s="7">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="E175" s="7">
-        <v>92.75</v>
+        <v>635.75</v>
       </c>
       <c r="F175" s="7">
-        <v>4.8377981239999999</v>
+        <v>5.2217808669999997</v>
       </c>
       <c r="G175" s="13" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="H175" s="14">
-        <v>88.47</v>
+        <v>604.20000000000005</v>
       </c>
       <c r="I175" s="6" t="s">
         <v>8</v>
@@ -9136,12 +9135,12 @@
       <c r="Y175" s="13"/>
       <c r="Z175" s="13"/>
     </row>
-    <row r="176" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A176" s="5">
-        <v>46241.688055555554</v>
+        <v>46244.635509259257</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C176" s="6" t="s">
         <v>7</v>
@@ -9150,16 +9149,16 @@
         <v>10</v>
       </c>
       <c r="E176" s="7">
-        <v>2720</v>
+        <v>977</v>
       </c>
       <c r="F176" s="7">
-        <v>4.8978017740000004</v>
+        <v>5.223478729</v>
       </c>
       <c r="G176" s="13" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="H176" s="14">
-        <v>2593</v>
+        <v>928.5</v>
       </c>
       <c r="I176" s="6" t="s">
         <v>8</v>
@@ -9182,30 +9181,30 @@
       <c r="Y176" s="13"/>
       <c r="Z176" s="13"/>
     </row>
-    <row r="177" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A177" s="5">
-        <v>46241.635567129626</v>
+        <v>46239.696701388886</v>
       </c>
       <c r="B177" s="6" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="C177" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D177" s="7">
+        <v>67</v>
+      </c>
+      <c r="E177" s="7">
+        <v>373</v>
+      </c>
+      <c r="F177" s="7">
+        <v>5.2483069980000003</v>
+      </c>
+      <c r="G177" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="E177" s="7">
-        <v>125.9</v>
-      </c>
-      <c r="F177" s="7">
-        <v>4.9166666670000003</v>
-      </c>
-      <c r="G177" s="13" t="s">
-        <v>160</v>
-      </c>
       <c r="H177" s="14">
-        <v>120</v>
+        <v>354.4</v>
       </c>
       <c r="I177" s="6" t="s">
         <v>8</v>
@@ -9228,30 +9227,30 @@
       <c r="Y177" s="13"/>
       <c r="Z177" s="13"/>
     </row>
-    <row r="178" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A178" s="5">
         <v>46244.63553240741</v>
       </c>
       <c r="B178" s="6" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C178" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D178" s="7">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E178" s="7">
-        <v>424</v>
+        <v>2690</v>
       </c>
       <c r="F178" s="7">
-        <v>5.1196231560000003</v>
+        <v>5.3662358010000002</v>
       </c>
       <c r="G178" s="13" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="H178" s="14">
-        <v>403.35</v>
+        <v>2553</v>
       </c>
       <c r="I178" s="6" t="s">
         <v>8</v>
@@ -9276,28 +9275,28 @@
     </row>
     <row r="179" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A179" s="5">
-        <v>46241.765462962961</v>
+        <v>46244.767650462964</v>
       </c>
       <c r="B179" s="6" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="C179" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D179" s="7">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E179" s="7">
-        <v>635.75</v>
+        <v>311</v>
       </c>
       <c r="F179" s="7">
-        <v>5.2217808669999997</v>
+        <v>5.4058634129999996</v>
       </c>
       <c r="G179" s="13" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="H179" s="14">
-        <v>604.20000000000005</v>
+        <v>295.05</v>
       </c>
       <c r="I179" s="6" t="s">
         <v>8</v>
@@ -9322,28 +9321,28 @@
     </row>
     <row r="180" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A180" s="5">
-        <v>46244.635509259257</v>
+        <v>46244.76730324074</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C180" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D180" s="7">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E180" s="7">
-        <v>977</v>
+        <v>210</v>
       </c>
       <c r="F180" s="7">
-        <v>5.223478729</v>
+        <v>5.5170334639999998</v>
       </c>
       <c r="G180" s="13" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="H180" s="14">
-        <v>928.5</v>
+        <v>199.02</v>
       </c>
       <c r="I180" s="6" t="s">
         <v>8</v>
@@ -9366,30 +9365,30 @@
       <c r="Y180" s="13"/>
       <c r="Z180" s="13"/>
     </row>
-    <row r="181" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A181" s="5">
-        <v>46239.696701388886</v>
+        <v>46244.635520833333</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="C181" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D181" s="7">
-        <v>67</v>
+        <v>200</v>
       </c>
       <c r="E181" s="7">
-        <v>373</v>
+        <v>244</v>
       </c>
       <c r="F181" s="7">
-        <v>5.2483069980000003</v>
+        <v>5.8568329720000003</v>
       </c>
       <c r="G181" s="13" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="H181" s="14">
-        <v>354.4</v>
+        <v>230.5</v>
       </c>
       <c r="I181" s="6" t="s">
         <v>8</v>
@@ -9412,30 +9411,30 @@
       <c r="Y181" s="13"/>
       <c r="Z181" s="13"/>
     </row>
-    <row r="182" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A182" s="5">
-        <v>46244.63553240741</v>
+        <v>46150.635416666664</v>
       </c>
       <c r="B182" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C182" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D182" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E182" s="7">
-        <v>2690</v>
+        <v>3810</v>
       </c>
       <c r="F182" s="7">
-        <v>5.3662358010000002</v>
+        <v>5.9274911030000004</v>
       </c>
       <c r="G182" s="13" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="H182" s="14">
-        <v>2553</v>
+        <v>3596.8</v>
       </c>
       <c r="I182" s="6" t="s">
         <v>8</v>
@@ -9458,30 +9457,30 @@
       <c r="Y182" s="13"/>
       <c r="Z182" s="13"/>
     </row>
-    <row r="183" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A183" s="5">
-        <v>46244.767650462964</v>
+        <v>46241.63554398148</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="C183" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D183" s="7">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E183" s="7">
-        <v>311</v>
+        <v>2710</v>
       </c>
       <c r="F183" s="7">
-        <v>5.4058634129999996</v>
+        <v>6.1496278889999996</v>
       </c>
       <c r="G183" s="13" t="s">
-        <v>142</v>
+        <v>185</v>
       </c>
       <c r="H183" s="14">
-        <v>295.05</v>
+        <v>2553</v>
       </c>
       <c r="I183" s="6" t="s">
         <v>8</v>
@@ -9509,25 +9508,25 @@
         <v>46244.76730324074</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C184" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D184" s="7">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E184" s="7">
-        <v>210</v>
+        <v>730</v>
       </c>
       <c r="F184" s="7">
-        <v>5.5170334639999998</v>
+        <v>6.1509379089999996</v>
       </c>
       <c r="G184" s="13" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="H184" s="14">
-        <v>199.02</v>
+        <v>687.7</v>
       </c>
       <c r="I184" s="6" t="s">
         <v>8</v>
@@ -9550,30 +9549,30 @@
       <c r="Y184" s="13"/>
       <c r="Z184" s="13"/>
     </row>
-    <row r="185" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A185" s="5">
-        <v>46244.635520833333</v>
+        <v>46244.63559027778</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C185" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D185" s="7">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="E185" s="7">
-        <v>244</v>
+        <v>773</v>
       </c>
       <c r="F185" s="7">
-        <v>5.8568329720000003</v>
+        <v>6.4005505850000004</v>
       </c>
       <c r="G185" s="13" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="H185" s="14">
-        <v>230.5</v>
+        <v>726.5</v>
       </c>
       <c r="I185" s="6" t="s">
         <v>8</v>
@@ -9596,30 +9595,30 @@
       <c r="Y185" s="13"/>
       <c r="Z185" s="13"/>
     </row>
-    <row r="186" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A186" s="5">
-        <v>46150.635416666664</v>
+        <v>46244.76730324074</v>
       </c>
       <c r="B186" s="6" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="C186" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D186" s="7">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E186" s="7">
-        <v>3810</v>
+        <v>310.5</v>
       </c>
       <c r="F186" s="7">
-        <v>5.9274911030000004</v>
+        <v>6.4814814810000003</v>
       </c>
       <c r="G186" s="13" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="H186" s="14">
-        <v>3596.8</v>
+        <v>291.60000000000002</v>
       </c>
       <c r="I186" s="6" t="s">
         <v>8</v>
@@ -9642,30 +9641,30 @@
       <c r="Y186" s="13"/>
       <c r="Z186" s="13"/>
     </row>
-    <row r="187" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A187" s="5">
-        <v>46241.63554398148</v>
+        <v>46240.687962962962</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="C187" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D187" s="7">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E187" s="7">
-        <v>2710</v>
+        <v>2770</v>
       </c>
       <c r="F187" s="7">
-        <v>6.1496278889999996</v>
+        <v>6.8260701890000002</v>
       </c>
       <c r="G187" s="13" t="s">
-        <v>185</v>
+        <v>144</v>
       </c>
       <c r="H187" s="14">
-        <v>2553</v>
+        <v>2593</v>
       </c>
       <c r="I187" s="6" t="s">
         <v>8</v>
@@ -9690,10 +9689,10 @@
     </row>
     <row r="188" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A188" s="5">
-        <v>46244.76730324074</v>
+        <v>46244.635509259257</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="C188" s="6" t="s">
         <v>7</v>
@@ -9702,16 +9701,16 @@
         <v>5</v>
       </c>
       <c r="E188" s="7">
-        <v>730</v>
+        <v>3980</v>
       </c>
       <c r="F188" s="7">
-        <v>6.1509379089999996</v>
+        <v>6.8456375840000003</v>
       </c>
       <c r="G188" s="13" t="s">
-        <v>151</v>
+        <v>188</v>
       </c>
       <c r="H188" s="14">
-        <v>687.7</v>
+        <v>3725</v>
       </c>
       <c r="I188" s="6" t="s">
         <v>8</v>
@@ -9734,30 +9733,30 @@
       <c r="Y188" s="13"/>
       <c r="Z188" s="13"/>
     </row>
-    <row r="189" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A189" s="5">
-        <v>46244.63559027778</v>
+        <v>46241.635567129626</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C189" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D189" s="7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E189" s="7">
-        <v>773</v>
+        <v>1424</v>
       </c>
       <c r="F189" s="7">
-        <v>6.4005505850000004</v>
+        <v>6.8667917449999996</v>
       </c>
       <c r="G189" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H189" s="14">
-        <v>726.5</v>
+        <v>1332.5</v>
       </c>
       <c r="I189" s="6" t="s">
         <v>8</v>
@@ -9782,28 +9781,28 @@
     </row>
     <row r="190" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A190" s="5">
-        <v>46244.76730324074</v>
+        <v>46241.765023148146</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C190" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D190" s="7">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="E190" s="7">
-        <v>310.5</v>
+        <v>219</v>
       </c>
       <c r="F190" s="7">
-        <v>6.4814814810000003</v>
+        <v>6.9074932880000004</v>
       </c>
       <c r="G190" s="13" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H190" s="14">
-        <v>291.60000000000002</v>
+        <v>204.85</v>
       </c>
       <c r="I190" s="6" t="s">
         <v>8</v>
@@ -9826,30 +9825,30 @@
       <c r="Y190" s="13"/>
       <c r="Z190" s="13"/>
     </row>
-    <row r="191" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A191" s="5">
-        <v>46240.687962962962</v>
+    <row r="191" spans="1:26" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A191" s="15" t="s">
+        <v>189</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C191" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D191" s="7">
-        <v>10</v>
-      </c>
-      <c r="E191" s="7">
-        <v>2770</v>
+        <v>30</v>
+      </c>
+      <c r="E191" s="8">
+        <v>974</v>
       </c>
       <c r="F191" s="7">
-        <v>6.8260701890000002</v>
+        <v>6.9154774970000004</v>
       </c>
       <c r="G191" s="13" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="H191" s="14">
-        <v>2593</v>
+        <v>911</v>
       </c>
       <c r="I191" s="6" t="s">
         <v>8</v>
@@ -9872,30 +9871,30 @@
       <c r="Y191" s="13"/>
       <c r="Z191" s="13"/>
     </row>
-    <row r="192" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A192" s="5">
-        <v>46244.635509259257</v>
+        <v>46244.63559027778</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C192" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D192" s="7">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="E192" s="7">
-        <v>3980</v>
+        <v>480</v>
       </c>
       <c r="F192" s="7">
-        <v>6.8456375840000003</v>
+        <v>7.1428571429999996</v>
       </c>
       <c r="G192" s="13" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="H192" s="14">
-        <v>3725</v>
+        <v>448</v>
       </c>
       <c r="I192" s="6" t="s">
         <v>8</v>
@@ -9918,30 +9917,30 @@
       <c r="Y192" s="13"/>
       <c r="Z192" s="13"/>
     </row>
-    <row r="193" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A193" s="5">
-        <v>46241.635567129626</v>
+        <v>46241.635520833333</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="C193" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D193" s="7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E193" s="7">
-        <v>1424</v>
+        <v>997</v>
       </c>
       <c r="F193" s="7">
-        <v>6.8667917449999996</v>
+        <v>7.3774905759999996</v>
       </c>
       <c r="G193" s="13" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H193" s="14">
-        <v>1332.5</v>
+        <v>928.5</v>
       </c>
       <c r="I193" s="6" t="s">
         <v>8</v>
@@ -9964,30 +9963,30 @@
       <c r="Y193" s="13"/>
       <c r="Z193" s="13"/>
     </row>
-    <row r="194" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A194" s="5">
-        <v>46241.765023148146</v>
+        <v>46244.76730324074</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C194" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D194" s="7">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E194" s="7">
-        <v>219</v>
+        <v>317</v>
       </c>
       <c r="F194" s="7">
-        <v>6.9074932880000004</v>
+        <v>7.4394170480000001</v>
       </c>
       <c r="G194" s="13" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H194" s="14">
-        <v>204.85</v>
+        <v>295.05</v>
       </c>
       <c r="I194" s="6" t="s">
         <v>8</v>
@@ -10010,30 +10009,30 @@
       <c r="Y194" s="13"/>
       <c r="Z194" s="13"/>
     </row>
-    <row r="195" spans="1:26" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A195" s="15" t="s">
         <v>189</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C195" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D195" s="7">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E195" s="8">
-        <v>974</v>
+        <v>214</v>
       </c>
       <c r="F195" s="7">
-        <v>6.9154774970000004</v>
+        <v>7.5268817200000004</v>
       </c>
       <c r="G195" s="13" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H195" s="14">
-        <v>911</v>
+        <v>199.02</v>
       </c>
       <c r="I195" s="6" t="s">
         <v>8</v>
@@ -10056,30 +10055,30 @@
       <c r="Y195" s="13"/>
       <c r="Z195" s="13"/>
     </row>
-    <row r="196" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A196" s="5">
-        <v>46244.63559027778</v>
+    <row r="196" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A196" s="15" t="s">
+        <v>189</v>
       </c>
       <c r="B196" s="6" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="C196" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D196" s="7">
-        <v>50</v>
-      </c>
-      <c r="E196" s="7">
-        <v>480</v>
+        <v>100</v>
+      </c>
+      <c r="E196" s="8">
+        <v>314</v>
       </c>
       <c r="F196" s="7">
-        <v>7.1428571429999996</v>
+        <v>7.6817558300000002</v>
       </c>
       <c r="G196" s="13" t="s">
-        <v>178</v>
+        <v>147</v>
       </c>
       <c r="H196" s="14">
-        <v>448</v>
+        <v>291.60000000000002</v>
       </c>
       <c r="I196" s="6" t="s">
         <v>8</v>
@@ -10102,30 +10101,30 @@
       <c r="Y196" s="13"/>
       <c r="Z196" s="13"/>
     </row>
-    <row r="197" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A197" s="5">
-        <v>46241.635520833333</v>
+        <v>46211.635416666664</v>
       </c>
       <c r="B197" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C197" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D197" s="7">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="E197" s="7">
-        <v>997</v>
+        <v>249</v>
       </c>
       <c r="F197" s="7">
-        <v>7.3774905759999996</v>
+        <v>8.0260303690000008</v>
       </c>
       <c r="G197" s="13" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H197" s="14">
-        <v>928.5</v>
+        <v>230.5</v>
       </c>
       <c r="I197" s="6" t="s">
         <v>8</v>
@@ -10148,30 +10147,30 @@
       <c r="Y197" s="13"/>
       <c r="Z197" s="13"/>
     </row>
-    <row r="198" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A198" s="5">
-        <v>46244.76730324074</v>
+    <row r="198" spans="1:26" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A198" s="15" t="s">
+        <v>189</v>
       </c>
       <c r="B198" s="6" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="C198" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D198" s="7">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="E198" s="7">
-        <v>317</v>
+        <v>986</v>
       </c>
       <c r="F198" s="7">
-        <v>7.4394170480000001</v>
+        <v>8.2327113060000006</v>
       </c>
       <c r="G198" s="13" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="H198" s="14">
-        <v>295.05</v>
+        <v>911</v>
       </c>
       <c r="I198" s="6" t="s">
         <v>8</v>
@@ -10195,29 +10194,29 @@
       <c r="Z198" s="13"/>
     </row>
     <row r="199" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A199" s="15" t="s">
-        <v>189</v>
+      <c r="A199" s="5">
+        <v>46181.635416666664</v>
       </c>
       <c r="B199" s="6" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C199" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D199" s="7">
-        <v>25</v>
-      </c>
-      <c r="E199" s="8">
-        <v>214</v>
+        <v>5</v>
+      </c>
+      <c r="E199" s="7">
+        <v>4040</v>
       </c>
       <c r="F199" s="7">
-        <v>7.5268817200000004</v>
+        <v>8.4563758389999997</v>
       </c>
       <c r="G199" s="13" t="s">
-        <v>156</v>
+        <v>188</v>
       </c>
       <c r="H199" s="14">
-        <v>199.02</v>
+        <v>3725</v>
       </c>
       <c r="I199" s="6" t="s">
         <v>8</v>
@@ -10240,30 +10239,30 @@
       <c r="Y199" s="13"/>
       <c r="Z199" s="13"/>
     </row>
-    <row r="200" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A200" s="15" t="s">
-        <v>189</v>
+    <row r="200" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A200" s="5">
+        <v>46244.76730324074</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C200" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D200" s="7">
-        <v>100</v>
-      </c>
-      <c r="E200" s="8">
-        <v>314</v>
+        <v>40</v>
+      </c>
+      <c r="E200" s="7">
+        <v>320.5</v>
       </c>
       <c r="F200" s="7">
-        <v>7.6817558300000002</v>
+        <v>8.6256566679999995</v>
       </c>
       <c r="G200" s="13" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H200" s="14">
-        <v>291.60000000000002</v>
+        <v>295.05</v>
       </c>
       <c r="I200" s="6" t="s">
         <v>8</v>
@@ -10286,30 +10285,30 @@
       <c r="Y200" s="13"/>
       <c r="Z200" s="13"/>
     </row>
-    <row r="201" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A201" s="5">
-        <v>46211.635416666664</v>
+        <v>46241.635567129626</v>
       </c>
       <c r="B201" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C201" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D201" s="7">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="E201" s="7">
-        <v>249</v>
+        <v>790</v>
       </c>
       <c r="F201" s="7">
-        <v>8.0260303690000008</v>
+        <v>8.7405368200000009</v>
       </c>
       <c r="G201" s="13" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="H201" s="14">
-        <v>230.5</v>
+        <v>726.5</v>
       </c>
       <c r="I201" s="6" t="s">
         <v>8</v>
@@ -10332,12 +10331,12 @@
       <c r="Y201" s="13"/>
       <c r="Z201" s="13"/>
     </row>
-    <row r="202" spans="1:26" ht="39" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A202" s="15" t="s">
-        <v>189</v>
+    <row r="202" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A202" s="5">
+        <v>46244.767627314817</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="C202" s="6" t="s">
         <v>7</v>
@@ -10346,16 +10345,16 @@
         <v>5</v>
       </c>
       <c r="E202" s="7">
-        <v>986</v>
+        <v>966</v>
       </c>
       <c r="F202" s="7">
-        <v>8.2327113060000006</v>
+        <v>8.8192663620000005</v>
       </c>
       <c r="G202" s="13" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="H202" s="14">
-        <v>911</v>
+        <v>896.9</v>
       </c>
       <c r="I202" s="6" t="s">
         <v>8</v>
@@ -10380,10 +10379,10 @@
     </row>
     <row r="203" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A203" s="5">
-        <v>46181.635416666664</v>
+        <v>46244.76730324074</v>
       </c>
       <c r="B203" s="6" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="C203" s="6" t="s">
         <v>7</v>
@@ -10392,16 +10391,16 @@
         <v>5</v>
       </c>
       <c r="E203" s="7">
-        <v>4040</v>
+        <v>435</v>
       </c>
       <c r="F203" s="7">
-        <v>8.4563758389999997</v>
+        <v>8.8861076350000001</v>
       </c>
       <c r="G203" s="13" t="s">
-        <v>188</v>
+        <v>158</v>
       </c>
       <c r="H203" s="14">
-        <v>3725</v>
+        <v>399.5</v>
       </c>
       <c r="I203" s="6" t="s">
         <v>8</v>
@@ -10424,30 +10423,30 @@
       <c r="Y203" s="13"/>
       <c r="Z203" s="13"/>
     </row>
-    <row r="204" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A204" s="5">
         <v>46244.76730324074</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C204" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D204" s="7">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="E204" s="7">
-        <v>320.5</v>
+        <v>749</v>
       </c>
       <c r="F204" s="7">
-        <v>8.6256566679999995</v>
+        <v>8.9137705389999997</v>
       </c>
       <c r="G204" s="13" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="H204" s="14">
-        <v>295.05</v>
+        <v>687.7</v>
       </c>
       <c r="I204" s="6" t="s">
         <v>8</v>
@@ -10472,28 +10471,28 @@
     </row>
     <row r="205" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A205" s="5">
-        <v>46241.635567129626</v>
+        <v>46239.789502314816</v>
       </c>
       <c r="B205" s="6" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="C205" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D205" s="7">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="E205" s="7">
-        <v>790</v>
+        <v>318</v>
       </c>
       <c r="F205" s="7">
-        <v>8.7405368200000009</v>
+        <v>9.0534979419999999</v>
       </c>
       <c r="G205" s="13" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="H205" s="14">
-        <v>726.5</v>
+        <v>291.60000000000002</v>
       </c>
       <c r="I205" s="6" t="s">
         <v>8</v>
@@ -10518,28 +10517,28 @@
     </row>
     <row r="206" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A206" s="5">
-        <v>46244.767627314817</v>
+        <v>46240.635601851849</v>
       </c>
       <c r="B206" s="6" t="s">
-        <v>9</v>
+        <v>129</v>
       </c>
       <c r="C206" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D206" s="7">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E206" s="7">
-        <v>976</v>
+        <v>548</v>
       </c>
       <c r="F206" s="7">
-        <v>8.8192663620000005</v>
+        <v>9.1850966330000006</v>
       </c>
       <c r="G206" s="13" t="s">
-        <v>143</v>
+        <v>200</v>
       </c>
       <c r="H206" s="14">
-        <v>896.9</v>
+        <v>501.9</v>
       </c>
       <c r="I206" s="6" t="s">
         <v>8</v>
@@ -10562,30 +10561,30 @@
       <c r="Y206" s="13"/>
       <c r="Z206" s="13"/>
     </row>
-    <row r="207" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A207" s="5">
-        <v>46244.76730324074</v>
+        <v>46244.63553240741</v>
       </c>
       <c r="B207" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C207" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D207" s="7">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E207" s="7">
-        <v>435</v>
+        <v>1170</v>
       </c>
       <c r="F207" s="7">
-        <v>8.8861076350000001</v>
+        <v>9.2436974789999997</v>
       </c>
       <c r="G207" s="13" t="s">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="H207" s="14">
-        <v>399.5</v>
+        <v>1071</v>
       </c>
       <c r="I207" s="6" t="s">
         <v>8</v>
@@ -10608,30 +10607,30 @@
       <c r="Y207" s="13"/>
       <c r="Z207" s="13"/>
     </row>
-    <row r="208" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A208" s="5">
-        <v>46244.76730324074</v>
-      </c>
-      <c r="B208" s="6" t="s">
-        <v>18</v>
+    <row r="208" spans="1:26" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A208" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="B208" s="9" t="s">
+        <v>26</v>
       </c>
       <c r="C208" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D208" s="7">
-        <v>11</v>
-      </c>
-      <c r="E208" s="7">
-        <v>749</v>
+        <v>40</v>
+      </c>
+      <c r="E208" s="10">
+        <v>996</v>
       </c>
       <c r="F208" s="7">
-        <v>8.9137705389999997</v>
+        <v>9.3304061469999997</v>
       </c>
       <c r="G208" s="13" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="H208" s="14">
-        <v>687.7</v>
+        <v>911</v>
       </c>
       <c r="I208" s="6" t="s">
         <v>8</v>
@@ -10655,8 +10654,8 @@
       <c r="Z208" s="13"/>
     </row>
     <row r="209" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A209" s="5">
-        <v>46239.789502314816</v>
+      <c r="A209" s="15" t="s">
+        <v>189</v>
       </c>
       <c r="B209" s="6" t="s">
         <v>14</v>
@@ -10667,11 +10666,11 @@
       <c r="D209" s="7">
         <v>100</v>
       </c>
-      <c r="E209" s="7">
-        <v>318</v>
+      <c r="E209" s="8">
+        <v>319</v>
       </c>
       <c r="F209" s="7">
-        <v>9.0534979419999999</v>
+        <v>9.3964334709999999</v>
       </c>
       <c r="G209" s="13" t="s">
         <v>147</v>
@@ -10700,30 +10699,30 @@
       <c r="Y209" s="13"/>
       <c r="Z209" s="13"/>
     </row>
-    <row r="210" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A210" s="5">
-        <v>46240.635601851849</v>
+    <row r="210" spans="1:26" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A210" s="15" t="s">
+        <v>189</v>
       </c>
       <c r="B210" s="6" t="s">
-        <v>129</v>
+        <v>26</v>
       </c>
       <c r="C210" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D210" s="7">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E210" s="7">
-        <v>548</v>
+        <v>1002</v>
       </c>
       <c r="F210" s="7">
-        <v>9.1850966330000006</v>
+        <v>9.9890230520000003</v>
       </c>
       <c r="G210" s="13" t="s">
-        <v>200</v>
+        <v>159</v>
       </c>
       <c r="H210" s="14">
-        <v>501.9</v>
+        <v>911</v>
       </c>
       <c r="I210" s="6" t="s">
         <v>8</v>
@@ -10746,30 +10745,30 @@
       <c r="Y210" s="13"/>
       <c r="Z210" s="13"/>
     </row>
-    <row r="211" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A211" s="5">
-        <v>46244.63553240741</v>
+    <row r="211" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A211" s="15" t="s">
+        <v>189</v>
       </c>
       <c r="B211" s="6" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="C211" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D211" s="7">
-        <v>11</v>
-      </c>
-      <c r="E211" s="7">
-        <v>1170</v>
+        <v>35</v>
+      </c>
+      <c r="E211" s="8">
+        <v>494</v>
       </c>
       <c r="F211" s="7">
-        <v>9.2436974789999997</v>
+        <v>10.26785714</v>
       </c>
       <c r="G211" s="13" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="H211" s="14">
-        <v>1071</v>
+        <v>448</v>
       </c>
       <c r="I211" s="6" t="s">
         <v>8</v>
@@ -10792,30 +10791,30 @@
       <c r="Y211" s="13"/>
       <c r="Z211" s="13"/>
     </row>
-    <row r="212" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A212" s="5">
-        <v>46241.63553240741</v>
+    <row r="212" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A212" s="15" t="s">
+        <v>189</v>
       </c>
       <c r="B212" s="6" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C212" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D212" s="7">
-        <v>9</v>
-      </c>
-      <c r="E212" s="7">
-        <v>1170</v>
+        <v>10</v>
+      </c>
+      <c r="E212" s="8">
+        <v>1024</v>
       </c>
       <c r="F212" s="7">
-        <v>9.2436974789999997</v>
+        <v>10.285406569999999</v>
       </c>
       <c r="G212" s="13" t="s">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="H212" s="14">
-        <v>1071</v>
+        <v>928.5</v>
       </c>
       <c r="I212" s="6" t="s">
         <v>8</v>
@@ -10838,30 +10837,30 @@
       <c r="Y212" s="13"/>
       <c r="Z212" s="13"/>
     </row>
-    <row r="213" spans="1:26" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A213" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="B213" s="9" t="s">
-        <v>26</v>
+      <c r="B213" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C213" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D213" s="7">
-        <v>40</v>
-      </c>
-      <c r="E213" s="10">
-        <v>996</v>
+        <v>25</v>
+      </c>
+      <c r="E213" s="7">
+        <v>220</v>
       </c>
       <c r="F213" s="7">
-        <v>9.3304061469999997</v>
+        <v>10.54165411</v>
       </c>
       <c r="G213" s="13" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H213" s="14">
-        <v>911</v>
+        <v>199.02</v>
       </c>
       <c r="I213" s="6" t="s">
         <v>8</v>
@@ -10884,30 +10883,30 @@
       <c r="Y213" s="13"/>
       <c r="Z213" s="13"/>
     </row>
-    <row r="214" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A214" s="15" t="s">
-        <v>189</v>
+    <row r="214" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A214" s="5">
+        <v>46241.635555555556</v>
       </c>
       <c r="B214" s="6" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="C214" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D214" s="7">
-        <v>100</v>
-      </c>
-      <c r="E214" s="8">
-        <v>319</v>
+        <v>3</v>
+      </c>
+      <c r="E214" s="7">
+        <v>3341</v>
       </c>
       <c r="F214" s="7">
-        <v>9.3964334709999999</v>
+        <v>10.629139070000001</v>
       </c>
       <c r="G214" s="13" t="s">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="H214" s="14">
-        <v>291.60000000000002</v>
+        <v>3020</v>
       </c>
       <c r="I214" s="6" t="s">
         <v>8</v>
@@ -10930,30 +10929,30 @@
       <c r="Y214" s="13"/>
       <c r="Z214" s="13"/>
     </row>
-    <row r="215" spans="1:26" ht="39" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A215" s="15" t="s">
-        <v>189</v>
+    <row r="215" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A215" s="5">
+        <v>46239.789502314816</v>
       </c>
       <c r="B215" s="6" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C215" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D215" s="7">
-        <v>5</v>
+        <v>150</v>
       </c>
       <c r="E215" s="7">
-        <v>1002</v>
+        <v>323</v>
       </c>
       <c r="F215" s="7">
-        <v>9.9890230520000003</v>
+        <v>10.768175579999999</v>
       </c>
       <c r="G215" s="13" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="H215" s="14">
-        <v>911</v>
+        <v>291.60000000000002</v>
       </c>
       <c r="I215" s="6" t="s">
         <v>8</v>
@@ -10976,30 +10975,30 @@
       <c r="Y215" s="13"/>
       <c r="Z215" s="13"/>
     </row>
-    <row r="216" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A216" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="B216" s="6" t="s">
-        <v>51</v>
+      <c r="B216" s="9" t="s">
+        <v>12</v>
       </c>
       <c r="C216" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D216" s="7">
-        <v>35</v>
-      </c>
-      <c r="E216" s="8">
-        <v>494</v>
+        <v>40</v>
+      </c>
+      <c r="E216" s="10">
+        <v>229</v>
       </c>
       <c r="F216" s="7">
-        <v>10.26785714</v>
+        <v>11.789113990000001</v>
       </c>
       <c r="G216" s="13" t="s">
-        <v>178</v>
+        <v>145</v>
       </c>
       <c r="H216" s="14">
-        <v>448</v>
+        <v>204.85</v>
       </c>
       <c r="I216" s="6" t="s">
         <v>8</v>
@@ -11022,30 +11021,30 @@
       <c r="Y216" s="13"/>
       <c r="Z216" s="13"/>
     </row>
-    <row r="217" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A217" s="15" t="s">
-        <v>189</v>
+    <row r="217" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A217" s="5">
+        <v>46239.793564814812</v>
       </c>
       <c r="B217" s="6" t="s">
-        <v>33</v>
+        <v>133</v>
       </c>
       <c r="C217" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D217" s="7">
-        <v>10</v>
-      </c>
-      <c r="E217" s="8">
-        <v>1024</v>
-      </c>
-      <c r="F217" s="7">
-        <v>10.285406569999999</v>
+        <v>23</v>
+      </c>
+      <c r="E217" s="7">
+        <v>890</v>
+      </c>
+      <c r="F217" s="15" t="e">
+        <v>#N/A</v>
       </c>
       <c r="G217" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="H217" s="14">
-        <v>928.5</v>
+        <v>201</v>
+      </c>
+      <c r="H217" s="16" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I217" s="6" t="s">
         <v>8</v>
@@ -11068,34 +11067,16 @@
       <c r="Y217" s="13"/>
       <c r="Z217" s="13"/>
     </row>
-    <row r="218" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A218" s="15" t="s">
-        <v>189</v>
-      </c>
-      <c r="B218" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C218" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D218" s="7">
-        <v>25</v>
-      </c>
-      <c r="E218" s="7">
-        <v>220</v>
-      </c>
-      <c r="F218" s="7">
-        <v>10.54165411</v>
-      </c>
-      <c r="G218" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="H218" s="14">
-        <v>199.02</v>
-      </c>
-      <c r="I218" s="6" t="s">
-        <v>8</v>
-      </c>
+    <row r="218" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A218" s="13"/>
+      <c r="B218" s="13"/>
+      <c r="C218" s="13"/>
+      <c r="D218" s="13"/>
+      <c r="E218" s="13"/>
+      <c r="F218" s="13"/>
+      <c r="G218" s="13"/>
+      <c r="H218" s="13"/>
+      <c r="I218" s="13"/>
       <c r="J218" s="13"/>
       <c r="K218" s="13"/>
       <c r="L218" s="13"/>
@@ -11114,34 +11095,16 @@
       <c r="Y218" s="13"/>
       <c r="Z218" s="13"/>
     </row>
-    <row r="219" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A219" s="5">
-        <v>46241.635555555556</v>
-      </c>
-      <c r="B219" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C219" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D219" s="7">
-        <v>3</v>
-      </c>
-      <c r="E219" s="7">
-        <v>3341</v>
-      </c>
-      <c r="F219" s="7">
-        <v>10.629139070000001</v>
-      </c>
-      <c r="G219" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="H219" s="14">
-        <v>3020</v>
-      </c>
-      <c r="I219" s="6" t="s">
-        <v>8</v>
-      </c>
+    <row r="219" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A219" s="13"/>
+      <c r="B219" s="13"/>
+      <c r="C219" s="13"/>
+      <c r="D219" s="13"/>
+      <c r="E219" s="13"/>
+      <c r="F219" s="13"/>
+      <c r="G219" s="13"/>
+      <c r="H219" s="13"/>
+      <c r="I219" s="13"/>
       <c r="J219" s="13"/>
       <c r="K219" s="13"/>
       <c r="L219" s="13"/>
@@ -11160,34 +11123,16 @@
       <c r="Y219" s="13"/>
       <c r="Z219" s="13"/>
     </row>
-    <row r="220" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A220" s="5">
-        <v>46239.789502314816</v>
-      </c>
-      <c r="B220" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C220" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D220" s="7">
-        <v>150</v>
-      </c>
-      <c r="E220" s="7">
-        <v>323</v>
-      </c>
-      <c r="F220" s="7">
-        <v>10.768175579999999</v>
-      </c>
-      <c r="G220" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="H220" s="14">
-        <v>291.60000000000002</v>
-      </c>
-      <c r="I220" s="6" t="s">
-        <v>8</v>
-      </c>
+    <row r="220" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A220" s="13"/>
+      <c r="B220" s="13"/>
+      <c r="C220" s="13"/>
+      <c r="D220" s="13"/>
+      <c r="E220" s="13"/>
+      <c r="F220" s="13"/>
+      <c r="G220" s="13"/>
+      <c r="H220" s="13"/>
+      <c r="I220" s="13"/>
       <c r="J220" s="13"/>
       <c r="K220" s="13"/>
       <c r="L220" s="13"/>
@@ -11206,34 +11151,16 @@
       <c r="Y220" s="13"/>
       <c r="Z220" s="13"/>
     </row>
-    <row r="221" spans="1:26" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A221" s="15" t="s">
-        <v>189</v>
-      </c>
-      <c r="B221" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C221" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D221" s="7">
-        <v>40</v>
-      </c>
-      <c r="E221" s="10">
-        <v>229</v>
-      </c>
-      <c r="F221" s="7">
-        <v>11.789113990000001</v>
-      </c>
-      <c r="G221" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="H221" s="14">
-        <v>204.85</v>
-      </c>
-      <c r="I221" s="6" t="s">
-        <v>8</v>
-      </c>
+    <row r="221" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A221" s="13"/>
+      <c r="B221" s="13"/>
+      <c r="C221" s="13"/>
+      <c r="D221" s="13"/>
+      <c r="E221" s="13"/>
+      <c r="F221" s="13"/>
+      <c r="G221" s="13"/>
+      <c r="H221" s="13"/>
+      <c r="I221" s="13"/>
       <c r="J221" s="13"/>
       <c r="K221" s="13"/>
       <c r="L221" s="13"/>
@@ -11252,34 +11179,16 @@
       <c r="Y221" s="13"/>
       <c r="Z221" s="13"/>
     </row>
-    <row r="222" spans="1:26" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A222" s="5">
-        <v>46239.793564814812</v>
-      </c>
-      <c r="B222" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="C222" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D222" s="7">
-        <v>23</v>
-      </c>
-      <c r="E222" s="7">
-        <v>890</v>
-      </c>
-      <c r="F222" s="15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G222" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="H222" s="16" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="I222" s="6" t="s">
-        <v>8</v>
-      </c>
+    <row r="222" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A222" s="13"/>
+      <c r="B222" s="13"/>
+      <c r="C222" s="13"/>
+      <c r="D222" s="13"/>
+      <c r="E222" s="13"/>
+      <c r="F222" s="13"/>
+      <c r="G222" s="13"/>
+      <c r="H222" s="13"/>
+      <c r="I222" s="13"/>
       <c r="J222" s="13"/>
       <c r="K222" s="13"/>
       <c r="L222" s="13"/>
@@ -32942,157 +32851,7 @@
       <c r="Y995" s="13"/>
       <c r="Z995" s="13"/>
     </row>
-    <row r="996" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A996" s="13"/>
-      <c r="B996" s="13"/>
-      <c r="C996" s="13"/>
-      <c r="D996" s="13"/>
-      <c r="E996" s="13"/>
-      <c r="F996" s="13"/>
-      <c r="G996" s="13"/>
-      <c r="H996" s="13"/>
-      <c r="I996" s="13"/>
-      <c r="J996" s="13"/>
-      <c r="K996" s="13"/>
-      <c r="L996" s="13"/>
-      <c r="M996" s="13"/>
-      <c r="N996" s="13"/>
-      <c r="O996" s="13"/>
-      <c r="P996" s="13"/>
-      <c r="Q996" s="13"/>
-      <c r="R996" s="13"/>
-      <c r="S996" s="13"/>
-      <c r="T996" s="13"/>
-      <c r="U996" s="13"/>
-      <c r="V996" s="13"/>
-      <c r="W996" s="13"/>
-      <c r="X996" s="13"/>
-      <c r="Y996" s="13"/>
-      <c r="Z996" s="13"/>
-    </row>
-    <row r="997" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A997" s="13"/>
-      <c r="B997" s="13"/>
-      <c r="C997" s="13"/>
-      <c r="D997" s="13"/>
-      <c r="E997" s="13"/>
-      <c r="F997" s="13"/>
-      <c r="G997" s="13"/>
-      <c r="H997" s="13"/>
-      <c r="I997" s="13"/>
-      <c r="J997" s="13"/>
-      <c r="K997" s="13"/>
-      <c r="L997" s="13"/>
-      <c r="M997" s="13"/>
-      <c r="N997" s="13"/>
-      <c r="O997" s="13"/>
-      <c r="P997" s="13"/>
-      <c r="Q997" s="13"/>
-      <c r="R997" s="13"/>
-      <c r="S997" s="13"/>
-      <c r="T997" s="13"/>
-      <c r="U997" s="13"/>
-      <c r="V997" s="13"/>
-      <c r="W997" s="13"/>
-      <c r="X997" s="13"/>
-      <c r="Y997" s="13"/>
-      <c r="Z997" s="13"/>
-    </row>
-    <row r="998" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A998" s="13"/>
-      <c r="B998" s="13"/>
-      <c r="C998" s="13"/>
-      <c r="D998" s="13"/>
-      <c r="E998" s="13"/>
-      <c r="F998" s="13"/>
-      <c r="G998" s="13"/>
-      <c r="H998" s="13"/>
-      <c r="I998" s="13"/>
-      <c r="J998" s="13"/>
-      <c r="K998" s="13"/>
-      <c r="L998" s="13"/>
-      <c r="M998" s="13"/>
-      <c r="N998" s="13"/>
-      <c r="O998" s="13"/>
-      <c r="P998" s="13"/>
-      <c r="Q998" s="13"/>
-      <c r="R998" s="13"/>
-      <c r="S998" s="13"/>
-      <c r="T998" s="13"/>
-      <c r="U998" s="13"/>
-      <c r="V998" s="13"/>
-      <c r="W998" s="13"/>
-      <c r="X998" s="13"/>
-      <c r="Y998" s="13"/>
-      <c r="Z998" s="13"/>
-    </row>
-    <row r="999" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A999" s="13"/>
-      <c r="B999" s="13"/>
-      <c r="C999" s="13"/>
-      <c r="D999" s="13"/>
-      <c r="E999" s="13"/>
-      <c r="F999" s="13"/>
-      <c r="G999" s="13"/>
-      <c r="H999" s="13"/>
-      <c r="I999" s="13"/>
-      <c r="J999" s="13"/>
-      <c r="K999" s="13"/>
-      <c r="L999" s="13"/>
-      <c r="M999" s="13"/>
-      <c r="N999" s="13"/>
-      <c r="O999" s="13"/>
-      <c r="P999" s="13"/>
-      <c r="Q999" s="13"/>
-      <c r="R999" s="13"/>
-      <c r="S999" s="13"/>
-      <c r="T999" s="13"/>
-      <c r="U999" s="13"/>
-      <c r="V999" s="13"/>
-      <c r="W999" s="13"/>
-      <c r="X999" s="13"/>
-      <c r="Y999" s="13"/>
-      <c r="Z999" s="13"/>
-    </row>
-    <row r="1000" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1000" s="13"/>
-      <c r="B1000" s="13"/>
-      <c r="C1000" s="13"/>
-      <c r="D1000" s="13"/>
-      <c r="E1000" s="13"/>
-      <c r="F1000" s="13"/>
-      <c r="G1000" s="13"/>
-      <c r="H1000" s="13"/>
-      <c r="I1000" s="13"/>
-      <c r="J1000" s="13"/>
-      <c r="K1000" s="13"/>
-      <c r="L1000" s="13"/>
-      <c r="M1000" s="13"/>
-      <c r="N1000" s="13"/>
-      <c r="O1000" s="13"/>
-      <c r="P1000" s="13"/>
-      <c r="Q1000" s="13"/>
-      <c r="R1000" s="13"/>
-      <c r="S1000" s="13"/>
-      <c r="T1000" s="13"/>
-      <c r="U1000" s="13"/>
-      <c r="V1000" s="13"/>
-      <c r="W1000" s="13"/>
-      <c r="X1000" s="13"/>
-      <c r="Y1000" s="13"/>
-      <c r="Z1000" s="13"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:Z222" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="S"/>
-      </filters>
-    </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Z222">
-      <sortCondition ref="F1"/>
-    </sortState>
-  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -33100,7 +32859,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DB11C0D-3E6F-42F5-B4A6-2F3ECF70CE76}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:N218"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -34174,7 +33932,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>76</v>
       </c>
@@ -34434,7 +34192,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>78</v>
       </c>
@@ -34486,7 +34244,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>63</v>
       </c>
@@ -34642,7 +34400,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>83</v>
       </c>
@@ -34668,7 +34426,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>79</v>
       </c>
@@ -34746,7 +34504,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>86</v>
       </c>
@@ -34824,7 +34582,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>83</v>
       </c>
@@ -34902,7 +34660,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>87</v>
       </c>
@@ -34951,10 +34709,10 @@
     Sheet1!$D:$D, D63,
     Sheet1!$E:$E, E63
 ) = 0, "NO MATCH IN TARGET", "MATCHED")</f>
-        <v>MATCHED</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+        <v>NO MATCH IN TARGET</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>79</v>
       </c>
@@ -35058,7 +34816,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>78</v>
       </c>
@@ -35214,7 +34972,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>83</v>
       </c>
@@ -35344,7 +35102,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>78</v>
       </c>
@@ -35370,7 +35128,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>94</v>
       </c>
@@ -35422,7 +35180,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>95</v>
       </c>
@@ -35448,7 +35206,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>96</v>
       </c>
@@ -35500,7 +35258,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>93</v>
       </c>
@@ -35526,7 +35284,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>90</v>
       </c>
@@ -35552,7 +35310,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>97</v>
       </c>
@@ -35656,7 +35414,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>60</v>
       </c>
@@ -35786,7 +35544,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>78</v>
       </c>
@@ -35838,7 +35596,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>80</v>
       </c>
@@ -35890,7 +35648,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>83</v>
       </c>
@@ -35916,7 +35674,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>99</v>
       </c>
@@ -35968,7 +35726,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="1">
         <v>46237.635567129626</v>
       </c>
@@ -35994,7 +35752,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>90</v>
       </c>
@@ -36020,7 +35778,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>83</v>
       </c>
@@ -36046,7 +35804,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>101</v>
       </c>
@@ -36072,7 +35830,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>102</v>
       </c>
@@ -36098,7 +35856,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>103</v>
       </c>
@@ -36124,7 +35882,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>104</v>
       </c>
@@ -36176,7 +35934,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>106</v>
       </c>
@@ -36228,7 +35986,7 @@
         <v>NO MATCH IN TARGET</v>
       </c>
     </row>
-    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>107</v>
       </c>
@@ -36254,7 +36012,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>108</v>
       </c>
@@ -36306,7 +36064,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>109</v>
       </c>
@@ -36332,7 +36090,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>110</v>
       </c>
@@ -36384,7 +36142,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>101</v>
       </c>
@@ -36410,7 +36168,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>111</v>
       </c>
@@ -36436,7 +36194,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>99</v>
       </c>
@@ -36462,7 +36220,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>112</v>
       </c>
@@ -36488,7 +36246,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>104</v>
       </c>
@@ -36514,7 +36272,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>104</v>
       </c>
@@ -36615,10 +36373,10 @@
     Sheet1!$D:$D, D127,
     Sheet1!$E:$E, E127
 ) = 0, "NO MATCH IN TARGET", "MATCHED")</f>
-        <v>MATCHED</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+        <v>NO MATCH IN TARGET</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>106</v>
       </c>
@@ -36644,7 +36402,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>101</v>
       </c>
@@ -36696,7 +36454,7 @@
         <v>NO MATCH IN TARGET</v>
       </c>
     </row>
-    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>115</v>
       </c>
@@ -36722,7 +36480,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>106</v>
       </c>
@@ -36748,7 +36506,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>99</v>
       </c>
@@ -36849,7 +36607,7 @@
     Sheet1!$D:$D, D136,
     Sheet1!$E:$E, E136
 ) = 0, "NO MATCH IN TARGET", "MATCHED")</f>
-        <v>MATCHED</v>
+        <v>NO MATCH IN TARGET</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
@@ -36904,7 +36662,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>104</v>
       </c>
@@ -36956,7 +36714,7 @@
         <v>NO MATCH IN TARGET</v>
       </c>
     </row>
-    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>101</v>
       </c>
@@ -36982,7 +36740,7 @@
         <v>NO MATCH IN TARGET</v>
       </c>
     </row>
-    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>100</v>
       </c>
@@ -37008,7 +36766,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>101</v>
       </c>
@@ -37034,7 +36792,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>117</v>
       </c>
@@ -37060,7 +36818,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>97</v>
       </c>
@@ -37086,7 +36844,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>117</v>
       </c>
@@ -37112,7 +36870,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>87</v>
       </c>
@@ -37138,7 +36896,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>99</v>
       </c>
@@ -37164,7 +36922,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>99</v>
       </c>
@@ -37190,7 +36948,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>101</v>
       </c>
@@ -37216,7 +36974,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>97</v>
       </c>
@@ -37242,7 +37000,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>69</v>
       </c>
@@ -37294,7 +37052,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>79</v>
       </c>
@@ -37320,7 +37078,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>118</v>
       </c>
@@ -37346,7 +37104,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>92</v>
       </c>
@@ -37372,7 +37130,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>97</v>
       </c>
@@ -37398,7 +37156,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>119</v>
       </c>
@@ -37424,7 +37182,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>79</v>
       </c>
@@ -37450,7 +37208,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>87</v>
       </c>
@@ -37476,7 +37234,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>120</v>
       </c>
@@ -37502,7 +37260,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>120</v>
       </c>
@@ -37528,7 +37286,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>87</v>
       </c>
@@ -37554,7 +37312,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>90</v>
       </c>
@@ -37580,7 +37338,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>113</v>
       </c>
@@ -37606,7 +37364,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>81</v>
       </c>
@@ -37632,7 +37390,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="167" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>83</v>
       </c>
@@ -37684,7 +37442,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>122</v>
       </c>
@@ -37733,10 +37491,10 @@
     Sheet1!$D:$D, D170,
     Sheet1!$E:$E, E170
 ) = 0, "NO MATCH IN TARGET", "MATCHED")</f>
-        <v>MATCHED</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+        <v>NO MATCH IN TARGET</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>97</v>
       </c>
@@ -37762,7 +37520,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>124</v>
       </c>
@@ -37814,7 +37572,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>97</v>
       </c>
@@ -37918,7 +37676,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="178" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>126</v>
       </c>
@@ -37944,7 +37702,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="179" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>78</v>
       </c>
@@ -37970,7 +37728,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="180" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>78</v>
       </c>
@@ -38048,7 +37806,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="183" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>79</v>
       </c>
@@ -38074,7 +37832,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="184" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>127</v>
       </c>
@@ -38100,7 +37858,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="185" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>83</v>
       </c>
@@ -38253,7 +38011,7 @@
     Sheet1!$D:$D, D190,
     Sheet1!$E:$E, E190
 ) = 0, "NO MATCH IN TARGET", "MATCHED")</f>
-        <v>MATCHED</v>
+        <v>NO MATCH IN TARGET</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
@@ -38308,7 +38066,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="193" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>113</v>
       </c>
@@ -38412,7 +38170,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>113</v>
       </c>
@@ -38464,7 +38222,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="199" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>83</v>
       </c>
@@ -38516,7 +38274,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="201" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" s="1">
         <v>46238.69059027778</v>
       </c>
@@ -38542,7 +38300,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="202" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A202" t="s">
         <v>116</v>
       </c>
@@ -38672,7 +38430,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="207" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A207" s="11" t="s">
         <v>69</v>
       </c>
@@ -38854,7 +38612,7 @@
         <v>MATCHED</v>
       </c>
     </row>
-    <row r="214" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A214" s="11" t="s">
         <v>113</v>
       </c>
@@ -38985,13 +38743,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="G1:G218" xr:uid="{2DB11C0D-3E6F-42F5-B4A6-2F3ECF70CE76}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="NO MATCH IN TARGET"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>